--- a/llm-classifier/results/llm_results_qwen2.5_14b-instruct.xlsx
+++ b/llm-classifier/results/llm_results_qwen2.5_14b-instruct.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N228"/>
+  <dimension ref="A1:N249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,12 +657,30 @@
 El trabajo hace parte de un proyecto de tesis doctoral que se propone desarrollar una arquitectura de integración de datos que sirva para implementar un lenguaje conceptual de recuperación de datos médicos. Como parte de la arquitectura de integración, se requiere implementar un wrapper que permita acceder a algunos de los atributos especificados en el estándar, para con base en ellos recuperar las imágenes y dar respuestas a consultas de usuario.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Information systems</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>The project focuses on developing an architecture for data integration and retrieval of medical images in DICOM format, which is a broad information-handling system rather than a specific database or web application.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Administración de datos, Integración de los datos, Recuperación de información</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>Bases de datos</t>
@@ -678,7 +696,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:01:52+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -765,12 +787,34 @@
 Como resultado se presenta la aplicación web PrediXaber11, donde las personas pueden acceder y ejecutar consultas. La aplicación usará la información suministrada del evaluado para entregar los posibles resultados en cada una de las áreas académicas evaluadas por el ICFES.</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Data mining</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a data-mining classifier to predict test results, and it includes the development of an application web where users can execute queries.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Sistemas de información, Minería de datos, Evaluación de personal docente, Universidad del Valle. Sede Tuluá</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>Minería de datos</t>
@@ -786,7 +830,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:02:07+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -809,12 +857,30 @@
           <t>En la actualidad las empresas utilizan gran cantidad de información, siendo un componente fundamental para las mismas [Pl99]. Las fuentes de datos son múltiples, y debido al crecimiento tecnológico global, enfáticamente en las ciencias de la computación, las redes sociales se han convertido en un recurso de gran importancia para las organizaciones [ELGF07]. La información que se encuentra en las redes sociales sobre compañías en particular, no solo es importante para ellas, sino también indispensable para las que usan dicha información como insumo para realizar análisis de mercado, imagen, preferencias, etc. [BSH09]. Por ejemplo, en Bogotá hay una empresa llamada Meridean que realiza estudios de Social Media para otras corporaciones a partir de información extra ‘ida de las redes sociales. El presente trabajo de grado, propone como solución, la construcción de un prototipo de clasificador semi-supervisado de texto, que ayudaría a automatizar (evitar labores manuales costosas y demoradas) el proceso de clasificación de información en la compañía. A partir de características (features) de los datos (comentarios de social media), el prototipo entrega los mismos, clasificados por categorías. Estas anotaciones obedecen a parámetros establecidos por Meridean. Para verificar la aplicabilidad del sistema, se realizaron pruebas de rendimiento al clasificador, las cuales se detallan en este documento.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Natural language processing</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>The project focuses on the semi-supervised classification of social media comments, which involves natural-language text processing and analysis.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Redes sociales, Comentarios, Clasificación, Mercadeo de la informacion</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>Inteligencia arificial</t>
@@ -830,7 +896,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:02:20+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -854,12 +924,30 @@
 </t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Information systems</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>The project focuses on developing an ECM system for managing digital information in academic coordinations, which falls under general information handling rather than a specific enterprise application or web/mobile platform.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Administración de contenidos digitales, Sistemas de información Web, Desarrollo de software</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -875,7 +963,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:02:34+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -898,12 +990,30 @@
           <t>Actualmente, la empresa Carvajal Tecnología y Servicios, tiene una serie de insuficiencias en la dependencia de tercerización de tecnología y outsourcing (ITO), donde se brindan servicios para satisfacer necesidades internas y a diferentes sectores de la industria, siendo la inducción a nuevos empleados y la operación del servicio, las problemáticas identificadas. En este sentido, actualmente dicha dependencia no dispone de un conducto regular sólido que le permita estructurar una capacitación de forma eficiente para los empleados nuevos. Además, en la operación del servicio no se cuenta con información centralizada, ocasionando pérdida de tiempo, reprocesos e incremento de los costos del negocio. En consecuencia, una posible solución a la problemática planteada es centralizar la información en un gestor de contenidos, apoyado en una plataforma tecnológica, con lo que al mismo tiempo, se apoyarán los procesos de gestión del conocimiento que internamente adelanta la empresa.</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>The project focuses on adapting an open-source platform to support the induction of new employees and centralize information for efficient service operations within Carvajal Tecnología y Servicios, which aligns with enterprise information systems.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Plataforma virtual, Tercerización de Tecnología, Gestión del conocimiento</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -919,7 +1029,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:02:49+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -943,12 +1057,34 @@
 </t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Image processing</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a web application that uses image processing techniques to support iridologists in diagnosing diseases.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Aplicaciones Web, Interpretación morfológica, Iridología, Diagnóstico de enfermedades</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>Procesamiento digital de imagenes</t>
@@ -964,7 +1100,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:03:02+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -987,12 +1127,30 @@
           <t>El principal objetivo de una arquitectura SSO (Single Sign On) es transferir la funcionalidad de autenticación propia de cada programa a un solo servicio de SSO. En una arquitectura SSO, todos los mecanismos de seguridad se encuentran concentrados en el SSO, siendo éste el único punto de autenticación en el sistema. Otro beneficio de una arquitectura Single Sign On es que los usuarios deben hacer el proceso de ingreso una sola vez a cada aplicación, a pesar de que continúan interactuando con múltiples componentes de seguridad en el sistema. El concepto Single Sign On no necesariamente se refiere a una sincronización de contraseñas, ya que en ese caso todas las aplicaciones y servicios funcionarían con una misma contraseña, pero no es una buena solución, ya que en lugar de fortalecer la seguridad, la estaría debilitando. Una implementación real de SSO, deberá contar con un agente SSO que se encarga de almacenar en una base de datos o directorio protegido los passwords que le permiten al usuario acceder a cada una de las aplicaciones o servicios, en el momento que lo desee, ya que el proceso de login se realiza de manera transparente al usuario, una vez que éste ha sido autenticado por medio de una arquitectura SSO.</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>The project focuses on implementing a centralized authentication and authorization system (SSO), which is a cybersecurity measure.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Autenticación, Autorización, Seguridad en los computadores, Sistemas centralizados, Arquitectura SSO</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>Seguridad</t>
@@ -1008,7 +1166,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:03:16+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1031,12 +1193,30 @@
           <t>El preprocesamiento de información tiene como propósito fundamental la “manipulación y transformación de los datos en bruto de manera que permita exponer o al menos facilitar la exposición de la información contenida en el arreglo de datos. [1]” Existen diversas herramientas que ofrecen la posibilidad de ejecutar subtareas de la extracci´on de informaci´on y procesamiento de lenguaje natural con este propósito, sin embargo son escasas aquellas que brindan la posibilidad de ejecutar más de una de estas tareas, esto sin mencionar que del mismo modo son escasas aquellas que permiten el tratamiento de datos en idiomas diferentes al inglés. Tomando como fuente de datos a procesar a Internet, debe considerarse que es una fuente inagotable de información, basta y no muy bien ordenada; no obstante dicha información debe tener cierto grado de orden para poder ser tratada por las subtareas de extracci´on de informaci´on y generar resultados útiles a partir de los datos procesados, como por ejemplo en el área del marketing para mejorar ventas o productos, analizar tendencias, entre otros. En el presente documento se expone el proceso de desarrollo de una aplicación que integra diferentes herramientas de preprocesamiento de información adaptadas para el idioma espa˜nol que toma como datos de entrada texto recuperado de la red social Twitter. Inicialmente se implementa un módulo que permite recuperar los documentos usando palabras clave como criterio de búsqueda. Así mismo se detalla la implementaci´on de m´odulos de corrección de palabras mal escritas, eliminaci´on de palabras vac´ıas, anotación gramatical, reconocimiento de nombres de entidades y el proceso realizado en su integración.</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Natural language processing</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a framework for text preprocessing from Twitter, including tasks such as correction of misspelled words, removal of stop words, grammatical annotation, and named entity recognition.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Framework (Programa para computadores), Procesamiento de textos, Twitter, Procesamiento del Lenguaje natural (computacion)</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>Procesamiento de lenguaje natural</t>
@@ -1052,7 +1232,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:03:32+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1075,12 +1259,30 @@
           <t>La programación por restricciones presenta estrategias de solución a problemas de optimización y combinatorios. La estrategia general para su uso es mediante la especificación de las variables del problema y las relaciones (restricciones) que entre ellas se deben mantener. Después de dicha especificación el usuario hace uso de motores de búsqueda predefinidos que se encargan de recorrer el espacio de soluciones del problema. Gecode es un componente de software que implementa el paradigma de programación por restricciones de manera eficiente. Sin embargo su utilización es compleja para usuarios por el lenguaje de programación. Oz es un lenguaje de programación inventado en la década de los 90 que soporta entre otros el paradigma de programación por restricciones. Debido a su concepción multiparadigma ha sido adoptado por una comunidad de investigación importante. Este lenguaje interpretado ofrece mejores abstracciones y provee un ambiente de trabajo más confortable. Su implementación, Mozart hasta ahora ha carecido de soporte en la adopción de los avances en la investigación en esta ´área. Por esta razón se ha diseñado una nueva máquina virtual con Gecode como motor de restricciones, para tomar ventaja de estos avances. En este documento se propondrán los mecanismos para la interacción de los motores de búsqueda implementados en Gecode con Mozart, como también los mecanismos que permitan al usuario implementar sus propios motores de búsqueda en Oz y utilizarlos. Esto es de gran importancia para los usuarios porque permitirá sacar ventaja del conocimiento que este posee sobre el problema obteniendo búsquedas más eficientes.</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Constraint programming</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>The project focuses on implementing constraint programming mechanisms using Gecode within the Mozart virtual machine, which is a clear example of constraint programming.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Programación con restricciones, Motores de búsqueda, Gecode</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>Programación por restricciones</t>
@@ -1096,7 +1298,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:03:45+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1119,12 +1325,30 @@
           <t>El presente documento describe el proceso realizado en torno al desarrollo de un trabajo de grado que tiene como propósito la implementación de una aplicación e-Learning 2.0 diseñada bajo conceptos de usabilidad y adaptabilidad. Aplicación que estará orientada a organizaciones de cualquier sector económico, que involucren procesos de formación y/o capacitación dentro de su planeación estratégica y sus objetivos misionales y visionales, de tal forma que éstas puedan adaptar y mantener su propia plataforma con base en sus necesidades, reduciendo así las barreras presentes en torno a las limitaciones geográficas que representan un aspecto importante para las organizaciones.</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>The project focuses on developing an e-Learning application for organizations with a strong emphasis on usability and adaptability.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>E-Learning, Tecnología de la información, Usabilidad, Adaptabilidad, Organizaciones</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1140,7 +1364,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:03:57+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1164,12 +1392,30 @@
 </t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>The project focuses on developing an educational software tool with an OVA to support primary school students in learning fractions, and it includes features typical of a Learning Management System (LMS).</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Desarrollo de software, Software educativo, Objetos Virtuales de Aprendizaje (OVA), Aprendizaje escolar, Números fraccionarios</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>Objeto virtual de aprendizaje</t>
@@ -1185,7 +1431,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:04:14+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1209,12 +1459,30 @@
 </t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Software engineering</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a tool to facilitate the coding of game scenarios for 2D video games, which falls under software development methodologies and tools.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Videojuegos, Desarrollo de software, Multiplataformas (programa para computador), Codificación</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>Juegos serios</t>
@@ -1230,7 +1498,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:04:28+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1253,12 +1525,30 @@
           <t>La Universidad del Valle sede Tuluá tiene la necesidad de disponer de un sistema de información para apoyar los procesos involucrados en el desarrollo del programa de práctica y/o pasantías para los estudiantes; se requiere de un herramienta que sirva como punto de confluencia en el establecimiento de relaciones con los diferentes actores que participan en la prestación de los servicios. Aunque las prácticas profesionales se formalizan a través de contratos de aprendizaje o convenios de práctica o pasantía, entre la universidad y la entidad externa, es indispensable apoyar el proceso a través de un sistema que permita centralizar la información de ofertas de las empresas, hojas de vida académicas de los estudiantes, además de dinamizar las tareas, mejorar la prestación del servicio apoyando las actividades de supervisión de los estudiantes en su primera experiencia laboral. Para solucionar exitosamente el problema, se hizo necesario realizar un proceso de ingeniería de software, en el que se analizaron cuáles serían la metodología y el modelo de desarrollo más adecuados según el procedimiento estándar definido por la Universidad del Valle y la dificultad que se quería resolver. Se decidió implementar un sistema de información web que permitiera a los diferentes actores interactuar y compartir de manejar fácil y eficazmente la información generada durante del proceso de consecución y desarrollo de las pasantías o prácticas profesionales. Posteriormente se realizaron las respectivas fases de análisis, diseño, implementación, pruebas y puesta en marcha del sistema siguiendo los lineamientos del modelo de desarrollo seleccionado. Finalmente se concluyó que con un sistema de información web para el apoyo a las pasantías y prácticas de los programas de pregrado de la Universidad del Valle sede Tuluá logra brindar una solución efectiva a la problemática presentada, obtenido resultados satisfactorios para los diferentes usuarios. Este documento sintetiza el trabajo realizado durante el desarrollado del proyecto.</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a web-based system to manage internships and practical training for students at Universidad del Valle, Sede Tuluá, which fits the definition of an enterprise information system.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Sistemas de información Web, Desarrollo de software, Pasantías, Prácticas académicas</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1274,7 +1564,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:04:44+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1299,7 +1593,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>full_text</t>
+          <t>metadata_only</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1313,10 +1607,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>The project focuses on developing a cost management application for the Hospital Psiquiátrico Universitario del Valle, which is a specific enterprise system designed to improve financial and administrative processes.</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>The project focuses on developing a cost management system for a specific hospital, which aligns with the definition of an enterprise information system.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Costos ABC, Sistema de Costos Basado en Actividades (ABC), Hospital Psiquiátrico Universitario del Valle</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1334,7 +1632,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-04-25T16:27:34+00:00</t>
+          <t>2026-04-26T15:04:58+00:00</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1657,30 @@
           <t>En este documento se detalla el proceso realizado como trabajo de grado consistente en la sistematización del control de asistencia docente de la Universidad del Valle sede Tuluá, el cual actualmente maneja el registro de los horarios, observaciones, cronogramas, reportes y el seguimiento del estado de las asistencias de los docentes de manera manual. Esta información se encuentra descentralizada, es difícil de administrar y el proceso es lento y dispendioso desperdiciando tiempo y recursos. Esta propuesta busca dar solución a los problemas anteriormente mencionados en el control de asistencia docente que opera en la Universidad, mediante la incorporación de un sistema de reconocimiento dactilar que registra y verifica las huellas de los docentes y permite su identificación única, garantizando la presencia del profesor a sus horas de clase. El sistema de reconocimiento dactilar se sincroniza con la plataforma informática encargada de la gestión del control de asistencia docente en la Universidad. Se generan reportes desde la aplicación con sus respectivos formatos de calidad para así facilitar el seguimiento y cumplimiento del cronograma de los docentes y aprovechar al máximo el uso de este aplicativo.</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>The project focuses on automating the attendance control process for teachers at Universidad del Valle, Sede Tuluá, which is a typical CRUD application for an institution.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Aplicaciones administrativas, Control de asistencia docente, Lector biométrico</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1380,7 +1696,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:05:12+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1404,12 +1724,30 @@
 </t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a social network for job and academic offers directed at university graduates, which is primarily a web application.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Redes sociales, Oferta laboral, Oferta académica</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1425,7 +1763,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:05:24+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1448,12 +1790,34 @@
           <t>Los procesos de selección de personal cada vez son más importantes para los empresarios que siempre buscan tomar decisiones adecuadas al momento de vincular personal a sus instituciones, la gran cantidad de aspirantes propicia que dicho proceso esté rodeado por un gran volumen de información que casi siempre se encuentra en medios físicos y por ende ocasiona demoras, confusión o desorganización en el proceso. Este trabajo se realiza con el fín de dar solución a problemas reales que se presentan en las actividades de reclutamiento y selección de personal dentro de las empresas, proporcionando un sistema de información web que además de sistematizar los mencionados procesos tiene la característica de recomendar aspirantes sin que se quiera desplazar el criterio humano de expertos o encargados de llevar a cabo actividades del proceso. Con base en lo anterior se plantea una solución combinando diversos conceptos y tecnologías, entre los aspectos más relevantes por mencionar se comenta que se integra el sistema de información web mencionado anteriormente con agentes de software que tienen como comportamiento principal generar una recomendación de aspirantes que se adhieran a un perfil determinado, también es importante mencionar que los agentes implementados aplican lógica difusa para producir su recomendación, de modo que con esto se logra eliminar subjetividades y sesgos que normalmente afectan negativamente las decisiones en un proceso de selección. Otros aspectos, tecnologías y conceptos para la realización de este proyecto se detallarán más adelante.</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Recommender systems</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Multi-agent systems</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>The project focuses on a recommendation system for personnel selection based on software agents, which integrates fuzzy logic to provide objective recommendations.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Selección de personal, Reclutamiento de personal, Sistemas de recomendación Web, Agentes de software</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1469,7 +1833,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:05:38+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1493,12 +1861,30 @@
 </t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>The project focuses on designing and implementing a CRM system for a call center company, which is a typical enterprise application.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Relaciones con el cliente, CRM, Plataforma digital, Contact Center Alopolis S.A.S.</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1514,7 +1900,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:05:51+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1539,7 +1929,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>full_text</t>
+          <t>metadata_only</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1553,12 +1943,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>The project focuses on developing a web application for Automotores Bejarano, providing services such as vehicle listings and customer management features.</t>
+          <t>The project focuses on developing a web application for a car dealership, providing services such as vehicle listings and customer management.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Aplicaciones Web, Portafolio multimedia, Concesionario Automotores Bejarano</t>
+          <t>Aplicaciones Web, Portafolio multimedia, Sistemas de gestión de información</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1578,7 +1968,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-04-25T16:28:43+00:00</t>
+          <t>2026-04-26T15:06:03+00:00</t>
         </is>
       </c>
     </row>
@@ -1620,12 +2010,34 @@
 tiempo establecido.</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Artificial intelligence</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a web-based system that uses genetic algorithms for vehicle location optimization, which falls under both Web applications and Artificial Intelligence.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Sistemas de información Web, Algoritmos genéticos, Tecnología de la información y de la comunicación. TIC</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>Inteligencia arificial</t>
@@ -1641,7 +2053,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:06:17+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1664,12 +2080,34 @@
           <t>El presente trabajo de grado tiene como objetivo implementar una herramienta que ayudará a fortalecer el proceso de aprendizaje de los niños con problemas de Discalculia (dificultad en el aprendizaje de las matemáticas) del CEET (Centro Educación Especial Tuluá) a través de una aplicación educativa web. En cumplimiento a este objetivo, se realizó una investigación acerca de las metodologías de enseñanza en niños con este problema, de igual forma se realizaron reuniones y se entrevistaron especialistas los cuales asesoraron de forma correcta el procedimiento que se debía realizar en la elección de la metodología indicada. Igualmente es importante destacar el uso de las TIC (Tecnologías de la información y comunicación) como herramientas de apoyo dando cumplimiento al objetivo del presente trabajo de grado. Por tal motivo se elaboraron OVAs (Objetos Virtuales de Aprendizaje), un sistema de recomendación donde se definió las rutas de aprendizaje de los niños y para la administración de la información de los usuarios y los OVAs, se realizó un LMS (Sistema de Gestión de Aprendizaje) manejando principios de diseño web y por ende asegurando el cumplimiento de principios básicos de navegabilidad, usabilidad y accesibilidad, garantizando que la interacción del usuario con ésta sea lo más agradable posible. Todo el proceso de elaboración de la aplicación se basó siguiendo una metodología de desarrollo ágil apropiada para asegurar todas las entrega en el tiempo establecido.</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Recommender systems</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>The project focuses on developing an educational web application for children with dyscalculia, incorporating virtual learning objects (OVAs) and a recommendation system to guide their learning paths.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Software educativo, Objetos Virtuales de Aprendizaje (OVA), Sistema de Gestión de Aprendizaje (LMS), Recomendación</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>Objeto virtual de aprendizaje</t>
@@ -1685,7 +2123,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:06:47+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1708,12 +2150,30 @@
           <t>Actualmente las empresas ya no se encuentran bajo el enfoque industrial, donde lo importante eran los activos físicos o tangibles, ahora se debe invertir esfuerzos en obtener y potenciar los activos intangibles; teniendo en cuenta que actualmente se vive en la era del conocimiento, donde los datos, la información y por ende la comunicación han pasado a ser determinantes en el éxito o fracaso de la gestión empresarial [34]. En consecuencia, la competitividad de las empresas está directamente relacionada con una buena gestión, donde la pregunta sería entonces ¿Cómo realizar una buena gestión?. El Balanced Scorecard (BSC) es un revolucionario método que apoya el proceso de gestión empresarial, dónde además de tener en cuenta la perspectiva financiera, también tiene en cuenta a los clientes, los procesos, la formación y crecimiento [34]. En este sentido, el presente proyecto ejecutado en modalidad de pasantía en la empresa Clip Consulting, permitió construir un producto de software que permitiera crear y administrar un BSC como apoyo al proceso de gestión empresarial, el cual será puesto en el mercado para los clientes de la empresa en cuestión.</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="H26" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a web application based on the Balanced Scorecard method to support strategic planning and improve productivity in companies.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Aplicaciones Web, Balanced scorecard (Gestión estratégica), Planificación estratégica</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1729,7 +2189,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:07:00+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1752,12 +2216,34 @@
           <t>Actualmente, la mayoría de empresas cuentan con Sistemas de Información Transaccionales para apoyar los procesos que ejecutan y gestionan cotidianamente. Pero, aunque las empresas posean un Sistema de Información Transaccional, sólo una minoría está consciente del valor de la información registrada por dichos Sistemas de Información, la cual puede ser utilizada por personas con cargos gerenciales para tomar así decisiones concernientes con el mejoramiento de procesos internos de la empresa como también determinaciones que a futuro dirijan el rumbo de la misma. Por lo anterior, surgieron los Sistemas de Información para el apoyo a la toma de decisiones, también conocidas como Aplicaciones de Inteligencia de Negocios, las cuales suplen la necesidad de los gerentes de poseer una herramienta que analice la información registrada en las bases de datos de los Sistemas de Información Transaccionales, para que las decisiones que tomen dichos gerentes tengan una mejor base y no solo sea una simple intuición. En el desarrollo de este proyecto se realizó un estudio en conjunto con la persona encargada de la toma de decisiones de las áreas de venta y mercadeo para elegir un conjunto de indicadores de desempeño claves para medir puntos de rendimiento que se determinaron como esenciales para su monitoreo. De manera paralela se fue desarrollando una aplicación web responsiva, la cual cuenta con una interfaz hecha con HTML5, siendo esto una característica que ayuda al desarrollo de software más simplificado de dicha interfaz. En conjunto, estos dos elementos brindan un apoyo a la toma de decisiones respecto a las áreas de venta y mercadeo del Call Center de la empresa BCS.</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Data mining</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a web application for business intelligence in sales and marketing, which involves data analysis and decision support.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Sistemas de información Web, Inteligencia de negocios, Toma de decisiones, Indicadores de desempeño, HTML5</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1773,7 +2259,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:07:15+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1796,12 +2286,34 @@
           <t>La Gestión del Conocimiento es un concepto aplicado en las organizaciones, que pretende transferir el conocimiento y experiencias existentes entre sus miembros, de modo que pueda ser utilizado como un recurso disponible para otros en la organización. Cualquier institución educativa puede verse como una organización que tiene como fin la educación y la formación académica, donde constantemente maneja un flujo de información, el cual representa un activo intangible muy valioso que en la mayoría de los casos no es correctamente gestionado. La plataforma que se desarrollará apoyará el proceso de gestión de conocimiento facilitando técnicas para capturar, organizar y almacenar el conocimiento que fluye en el colegio San Francisco de Asís, para transformarlo en un activo intelectual que represente beneficios académicos y se pueda compartir con cualquier persona. De esta manera se generará una comunidad virtual que permitirá que se mejoren las relaciones docente-estudiante, promueva la interacción social, el aprendizaje colaborativo y se administren correctamente todas las habilidades y experiencias tanto de docentes como de estudiantes haciendo del aprendizaje un proceso más ameno e interactivo.</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Information systems</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a web platform to support knowledge management and foster virtual community building in an educational institution.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Plataforma Web, Gestión del conocimiento, Comunidades virtuales</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1817,7 +2329,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:07:27+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1841,12 +2357,30 @@
 </t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a system for managing undergraduate projects and anteproyectos at Universidad del Valle, which is a CRUD application tailored to an institution's needs.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Sistemas de información para la gestión, Desarrollo de software, Proyectos de grado</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1862,7 +2396,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:07:41+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1886,12 +2424,30 @@
 </t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="H30" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a CRM system for C.E.A. Auto Ríos to manage customer relationships and operational processes, which aligns with the definition of an enterprise information system.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Relaciones con el cliente, CRM, Tecnología de la información y de la comunicación, Sistemas de información Web, Fidelización del cliente, Procesos operativos</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1907,7 +2463,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:07:59+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1930,12 +2490,30 @@
           <t>El propósito de este proyecto surgió de la necesidad de la Empresa Ingenio Carmelita S.A para controlar los activos de información que se manejan en la compañía y además de dar una solución correcta para aquellos activos de información más susceptibles a incidentes como lo son los de hardware y software. Por medio de la metodología de desarrollo RUP (Rational Unified Process) se realizaron las diferentes actividades que permitieron la identificación de los activos y de los diferentes incidentes a los que están expuestos estos, posteriormente se realizó el proceso de diseño y construcción de la aplicación que permitiera suplir los requisitos planteados. Para lo anterior se logró construir una aplicación web con la capacidad de gestionar los activos de información de la empresa de una forma fácil y eficiente, y el cual permitió guardar en la bases de datos de la empresa la referencia de los activos importantes, así como el control de la trazabilidad o movimientos de los mismos. Además permite el registro y respuesta a los incidentes de hardware y software logrando llevar un control sobre estos incidentes.</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a web-based system for managing information assets in a specific company, which aligns with the definition of an enterprise information system.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Sistemas de información Web, Activos de información, Metodología de desarrollo RUP (Rational Unified Process), Administración de activos</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1951,7 +2529,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:08:14+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1975,12 +2557,30 @@
 </t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a Balanced Scorecard software for COFINCAFÉ, an organization in the solidarity economy sector, to improve strategic management and decision-making processes.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Desarrollo de software, Balanced scorecard (Gestión estratégica), Sistemas de gestión, Cooperativa de ahorro y crédito Cafetera COFINCAFE</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1996,7 +2596,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:08:30+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2020,12 +2624,34 @@
 Además, la aplicación web utiliza un agente de recomendación que es capaz de soportar las fases del proceso de compra al ayudar a los clientes a realizar sus pedidos por medio de recomendaciones de productos. Este agente, hace uso de sistemas de filtrado colaborativo, que utilizan elementos como: la totalidad de los productos que se ofrecen, historiales de compras propios y de otros usuarios, similitudes entre los perfiles de usuarios y correlación entre los diferentes productos, los cuales son necesarios para el cálculo de recomendaciones y similitudes de un conjunto de productos [2, 29].</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mobile applications</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Recommender systems</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a mobile-accessible web application for order management that includes a recommendation agent using collaborative filtering techniques.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Aplicaciones Web, Dispositivos móviles, Sistemas de recomendación Web</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>Sistemas de recomendación</t>
@@ -2041,7 +2667,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:08:43+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2065,12 +2695,30 @@
 </t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="H34" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>The project focuses on designing and implementing a web-based system for managing requests and complaints from employees, customers, and suppliers of contracting companies in the BPO service.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Sistemas de información, Sistemas de información Web, Autogestión, Tercerización de Tecnología y Outsourcing (ITO), Procesos de Back Office (BPO)</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -2086,7 +2734,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:09:00+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2110,12 +2762,30 @@
 </t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="H35" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>The project focuses on developing an integrated system for academic scheduling, attendance control, and faculty payroll at Universidad del Valle Sede Buga, which fits the definition of a CRUD application for institutional management.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Sistemas de información, Programación académica, Nómina docente, Data Warehouse, Toma de decisiones</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -2131,7 +2801,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:09:17+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2155,12 +2829,30 @@
 </t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="H36" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>The project focuses on developing and implementing a management system for Conectic S.A.S., which includes CRM, customer management, contract creation, and employee evaluation processes.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Sistemas de información Web, Gestión de procesos, Indicadores de desempeño, Telecomunicaciones, Empresas de telecomunicaciones</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -2176,7 +2868,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:09:40+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2202,12 +2898,30 @@
 Finalmente, con el desarrollo de la interfaz prototipo se busca crear un diseño practico para ingresar la información que el Algoritmo Genético necesita. La interfaz fue desarrollado con el Framework (marco de trabajo) Ruby on Rails.</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Artificial intelligence</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="H37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>The project focuses on the development of a Genetic Algorithm for scheduling, which falls under artificial intelligence techniques.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Algoritmos genéticos, Asignación de agendas, Sistemas de información</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>Inteligencia arificial</t>
@@ -2223,7 +2937,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:09:51+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2246,12 +2964,30 @@
           <t>Actualmente los dispositivos de video capturan una gran cantidad de información de alguna escena del mundo real para procesarlos en sistemas de cómputo. A medida que aumenta la cantidad de información, se desarrollan técnicas de compresión para representar la información del video en la menor cantidad de bits posibles y facilitar su almacenamiento y transmisión. En los esfuerzos para maximizar la compresión de video, los grupos de estanzadización ITU-T Video Coding Experts Group (VCEG)1 en conjunto con la ISO/IEC MovingPicture Experts Group (MPEG)2 desarrollaron la recomendación H.265, conocida como High Efficiency Video Coding (HEVC) 3, que ha permitido incrementar la eficiencia de codificación,conservando la calidad de video con una menor tasa de bits, en comparación con estándaresanteriores [1] como el H.264/AVC, el H.263/CHC, el MPEG-4 ASP y el MPEG-2 H.262 MP.</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Image processing</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="H38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>The project focuses on motion estimation in HEVC using parallel programming, which falls under image processing techniques.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Programación paralela, Estimacion de movimiento, High Efficiency Video Coding (HEVC), Graphics Unit Processor (GPU)</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>Procesamiento digital de imagenes</t>
@@ -2267,7 +3003,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:10:04+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2291,12 +3031,30 @@
 </t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="H39" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>The project focuses on enriching the semantic content of an LMS to consume Linked Data from the Web, which falls under e-learning and leverages semantic web technologies.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Administración de contenidos Web, Web Semántica, Sistemas de información Web, Campus virtual, Moodle</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>Minería de datos</t>
@@ -2312,7 +3070,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:41:48+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2336,12 +3098,30 @@
 </t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="H40" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>The project focuses on designing and implementing an educational software tool for primary school students, accessible via a web page, which aligns with the definition of e-learning.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Software educativo, Enseñanza del lenguaje, Educación primaria</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -2357,7 +3137,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:10:33+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2381,12 +3165,30 @@
 </t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Information systems</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="H41" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>The project focuses on developing an information system to support the evaluation process of teaching staff, which falls under general information handling and does not fit into more specific categories like database management or enterprise applications.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Sistemas de información, Evaluación de personal docente, Universidad del Valle. Sede Tuluá</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -2402,7 +3204,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:10:48+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2426,12 +3232,30 @@
 </t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="H42" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>The project focuses on automating administrative processes for the Urban Curatorship of Tuluá, specifically for issuing urban licenses and providing public access to process status via a web solution.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Automatización de procesos, Procesos administrativos, Curadurías urbanas, Licencias urbanísticas</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -2447,7 +3271,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:11:03+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2471,12 +3299,30 @@
 </t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+      <c r="H43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>The project focuses on automating processes and improving decision-making for a specific company, SISA Soluciones Integrales En Salud, which fits the definition of an enterprise information system.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Automatización de procesos, Toma de decisiones, Sistemas de información Web</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -2492,7 +3338,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:11:17+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2516,12 +3366,30 @@
 </t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="H44" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a web application to support the quality management system of the Chamber of Commerce in Tuluá, addressing administrative and reporting needs.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Aplicaciones Web, Sistema de Gestión de Calidad (SGC), Java (Lenguaje de programación), JavaScript (Lenguaje de Programacion), HTML (Lenguaje de procesamiento de texto)</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -2537,7 +3405,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:11:34+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2921,12 +3793,30 @@
           <t>Actualmente se destacan muchas empresas dentro del sector de consultoría ambiental, las cuales prestan servicios profesionales y se encargan de asesorar a otras empresas en una o muchas áreas especificas que comprende el estudio de emisión de gases atmosféricos, calidad del aire, aguas residuales, ruido, entre otros. Estas empresas llevan a cabo un proceso de planeación para realizar la prestación de este servicio, con el fin abarcar detalladamente este proceso se tomó como referencia la empresa Incoambiental S.A.S. Con el objetivo de apoyar la prestación de este servicio y sus actividades en la planeación del mismo. Debido a que algunas de las tareas como la asignación de la consultoría se lleva actualmente de forma manual y la información no está centralizada, esto produce pérdida de tiempo, costos adicionales, realización de tareas que no son necesarias y reprocesos. Para la problemática planteada anteriormente se propuso la implementación de un sistema de información web para empresas que brindan el servicio de consultoría, con el fin de apoyar el proceso de planeación en la prestación del mismo, esta aplicación facilita la organización en las actividades que deben realizar los encargados de este servicio, el acceso a los formatos requeridos para este proceso, el control de los elementos que pertenecen al área de almacén, igualmente la generación de reportes para seguimiento de las actividades.</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+      <c r="H50" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a web-based system to support planning processes for operations and inventory management in Incoambiental S.A.S., which fits the definition of an enterprise information system.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Sistemas de información Web, Consultoría de empresas, Planificación de actividades, Operaciones, Asignación de tareas</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -2942,7 +3832,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:11:50+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2970,12 +3864,30 @@
           <t>En este trabajo se presenta Ecclesia, un sistema de información web para la gestión de procesos parroquiales que combina funcionalidades de administración de la información, eventos, seguimiento de estudiantes y determinación de ingresos. Ecclesia se fundamenta en un estudio del trabajo realizado diariamente en la Parroquia San Martín de Porres de Tuluá Valle del Cauca, a fin de analizar y determinar los motivos que generaban retardos en las actividades a desarrollar e ineficiencia en los canales de comunicación entre el personal. Para la recolección de datos fueron aplicadas tres técnicas, (I) la observación directa, (II) la entrevista no estructurada y (III) revisión documental. Los resultados obtenidos del estudio hicieron concientizar a la Parroquia de la necesidad de adoptar las nuevas tecnologías de la información como herramientas que permiten realizar un uso adecuado de los recursos, el tiempo, la información, entre otros. La solución tecnológica desarrollada permite la reducción en los tiempos de respuesta de los procesos parroquiales, enfatizando especialmente la actividad sacramental orientada a los feligreses. Además asiste en la toma de decisiones presentando la información contenida de manera oportuna, es decir que permite la extracción de información real en el momento que se requiera.</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+      <c r="H51" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a web-based system for managing processes and controlling activities in a specific parish, which aligns with the definition of an enterprise information system.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Sistemas de Información Administrativa, Gestión de procesos, Control de actividades</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -2991,7 +3903,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:12:04+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3020,12 +3936,34 @@
           <t>El presente proyecto se basó en una problemática que se genera alrededor de la gestión de los libros reglamentarios, la cual permite evidenciar en su desarrollo un considerable esfuerzo de parte de los docentes, dado que dicha gestión se realiza de forma manual ao a través de herramientas ofimáticas. Este proceso es costoso en tiempo e ineficiente. El análisis es lento, difícil y propenso a errores por lo que no permite identificar problemas y mucho menos oportunidades de mejoramiento por parte de los docentes y directivos docentes, dicha problemática está presente en la Institución Educativa María Antonia Ruiz. Para dar solución al problema propuesto se realizó el análisis, diseño e implementación de un sistema de información compuesto de una aplicación desktop, aplicación móvil y aplicación web para los procesos de libros reglamentarios, todo esto relacionado con la programación académica de la Institución. El proyecto se desarrolló basado en la metodología ICONIX y el patrón arquitectónico Modelo-Vista-Controlador (MVC), permitiendo así la creación de componentes robustos a su vez permitiendo la escalabilidad del mismo. También facilitó la realización de pruebas a lo largo del proceso y garantizando un producto final que cumpliera con las funcionalidades requeridas, ofrece mecanismos para la gestión de año lectivo, la gestión de planes de aula, diarios de clase y novedades en el aula.</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>The project focuses on developing an enterprise-level system for managing regulatory books and academic scheduling at a specific educational institution, with components including desktop, mobile, and web applications.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Sistemas de información Web, Aplicaciones móviles, Libros reglamentarios, Programación académica</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -3041,7 +3979,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:12:19+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3069,12 +4011,30 @@
           <t>En la empresa Área Informática S.A.S, se llevaban a cabo muchos procesos de forma manual, esto conllevó a retrasos y descontrol sobre la información que se generaba en los diferentes procedimientos. Se vio entonces, la necesidad de ayudar a mejorar estos procesos aportando los conocimientos adquiridos, buscando mejoras significativas en función de la calidad. Se realizó un análisis, diseño e implementación para un sistema de información el cual ayudó a la empresa a gestionar los procesos relacionados con las órdenes de servicio, se desarrolló un mecanismo el cual permitió generar la agenda de trabajo partiendo de la prioridad de los servicios que solicitan los clientes y de la disponibilidad de los técnicos, con la posibilidad de generar reportes estadísticos, sobre el estado de los procesos de Área Informática S.A.S. Y de esta forma mejorar la calidad en los procesos que se llevan a cabo en esta empresa.</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+      <c r="H53" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>The project focuses on developing an information system for managing service orders in a specific company, which aligns with the definition of enterprise information systems.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Sistemas de información en administración, Órdenes de servicio, Planificación de Recursos Empresariales (ERP), Área Informática S.A.S</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -3090,7 +4050,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:12:34+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3120,12 +4084,30 @@
           <t>En el presente documento se muestra el desarrollo de una herramienta de software diseñando e implementando objetos virtuales de aprendizaje (OVA) como apoyo al proceso de enseñanza-aprendizaje del programa de Manejo Ambiental para los estudiantes de grado once de la Institución Educativa Técnica La Marina en el área de Desechos de Producción Agropecuaria; este trabajo involucró la implementación del sistema de aprendizaje (LMS) Chamilo, que permitió alojar y acceder a diferentes actividades de aprendizaje independientes en varios formatos. Además, este ofrece mecanismos para la gestión de usuarios, grupos, cursos, colecciones y/o notas generadas por la interacción de los estudiantes con la evaluación de los OVA implementados.</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+      <c r="H54" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>The project focuses on developing educational software and virtual learning objects for teaching environmental management to high school students, using a Learning Management System (LMS) like Chamilo.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Software educativo, Objetos Virtuales de Aprendizaje (OVA), Sistemas de aprendizaje</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>Objeto virtual de aprendizaje</t>
@@ -3141,7 +4123,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:12:49+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3171,12 +4157,30 @@
           <t>En el presente documento se muestra el desarrollo de una herramienta de software diseñada como apoyo en el proceso de enseñanza-aprendizaje del idioma inglés en el grado décimo de la Institución Educativa Gimnasio del Pacífico, (Tuluá- Valle); para estos se utilizó el Sistema de Gestión de Aprendizaje (LMS) Moodle que permitió el alojamiento y acceso a viarias actividades de aprendizaje, además de permitir la integración de plugin de tipo de preguntas, el manejo de gestión de usuarios, grupos, cursos y calificaciones generadas por la iteración de los estudiantes con las evaluaciones. Se crearon materiales educativos empaquetados (OVA) con el fin de usarlos en la plataforma de aprendizaje, bajo el estándar Scorm.</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+      <c r="H55" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>The project focuses on developing an educational software tool using a Learning Management System (LMS) and Objectives Virtual of Learning (OVA) for teaching English in the tenth grade.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Objetos Virtuales de Aprendizaje, Sistema de Gestión de Aprendizaje, Inglés, Aprendizaje y enseñanza de idiomas</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>Objeto virtual de aprendizaje</t>
@@ -3192,7 +4196,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:13:05+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3221,12 +4229,30 @@
           <t>El presente trabajo de grado consiste en el reconocimiento de las señas estáticas del abecedario del Lenguaje de Señas colombiano (LSC) con el fin de promover la inclusión social de las personas con diversidad funcional en el habla por medio de la tecnología. El proyecto se desarrolló bajo la metodología de Proceso Unificado Ágil (AUP), adoptando una arquitectura Modelo Vista Controlador (MVC) y un paradigma de programación orientado a objetos en la codificación. En su implementación se utilizan técnicas de procesamiento digital de imágenes para la segmentación, el mejoramiento de la imagen y proyección de contornos para la extracción de características. La clasificación de la seña se realiza por medio del algoritmo Dynamic Time Warping (DTW). Como resultado, el sistema logro reconocer en promedio el 79% de las señas estáticas con una desviación estándar del 6%.</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Image processing</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+      <c r="H56" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>The project focuses on the recognition of static signs from the Colombian Sign Language alphabet using image processing techniques such as segmentation, image enhancement, and contour projection.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Lenguje de señas colombiano (LSC), Sistema de reconocimiento de señas, Procesamiento digital de imágenes</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>Procesamiento digital de imagenes</t>
@@ -3242,7 +4268,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:13:20+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3328,12 +4358,30 @@
           <t>El presente trabajo de grado de Ingeniería de Sistemas en la Universidad del Valle sede Tuluá, tuvo como propósito identificar los activos de información de la empresa SOMEC S.A., así como también determinar las falencias en el actual manejo de estos, teniendo en cuenta que los activos de información son una parte muy importante en el funcionamiento idóneo de las organizaciones y empresas, su buen manejo genera una ventaja competitiva. Para dar cumplimiento a este objetivo se utilizó la metodología ágil XP (eXtreme Programming), apoyándose también en gerencia de procesos de negocio (BPM).</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+      <c r="H58" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a web-based system for managing business processes and information assets in the company SOMEC S.A., which aligns with enterprise information systems.</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Sistemas de información Web, Activos de información, Gerencia de procesos de negocio (BPM), eXtreme Programming</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -3349,7 +4397,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:13:34+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3381,12 +4433,30 @@
           <t>En este trabajo de grado se implementó una aplicación web para la Institución Educativa Tulio Enrique Tascón de la ciudad de Buga con Objetos Virtuales de Aprendizaje (OVA) para la enseñanza de contenidos contables de los grados sexto y séptimo e implementar una extensión en el LMS Moodle para evaluación de los temas contables. Esta aplicación es un complemento teórico práctico, está compuesta y diseñada por diferentes actividades con el fin de dar apoyo a los profesores en la enseñanza de contenidos contables.</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="H59" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>The project focuses on implementing a web application with virtual learning objects and an extension for Moodle, which is explicitly aimed at supporting the teaching of accounting concepts in secondary education.</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Aplicaciones Web, Objetos Virtuales de Aprendizaje (OVA), Moodle</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>Objeto virtual de aprendizaje</t>
@@ -3402,7 +4472,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:13:48+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3483,12 +4557,30 @@
           <t>El presente documento de trabajo de grado se describe el desarrollo una herramienta que incorpora OVA (Objetos Virtuales de Aprendizaje), para el apoyo a la enseñanza de la materia de Trigonometría de la Institución Educativa Leonor Lourido de Yumbo, Valle del Cauca; esta implementación involucró la investigación de un sistema de aprendizaje (LMS), que permite alojar y acceder libremente a los contenidos de las diversas actividades de aprendizaje. Esta herramienta es un complemento teórico práctico a los contenidos dictados en la Institución Educativa Leonor Lourido y se compone de definiciones teóricas con sus respectivos ejemplos, seguidos de actividades interactivas para los estudiantes, además de tareas asignadas para reforzar los conocimientos adquiridos.</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+      <c r="H61" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>The project focuses on developing OVA for teaching trigonometry and integrating them into an LMS, which aligns with e-learning artifacts.</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Objetos Virtuales de Aprendizaje (OVA), Trigonometría, Sistemas de aprendizaje, Ambientes virtuales de aprendizaje</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>Objeto virtual de aprendizaje</t>
@@ -3504,7 +4596,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:14:03+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3664,12 +4760,34 @@
           <t>El presente trabajo consiste en la evaluación de figuras acrobáticas que se usan en la creación de coreografías de baile. Tiene como objetivo principal, convertirse en una herramienta de apoyo para mujeres (docentes) que enseñan danzas, debido a que por su estructura física pueden versen limitadas en el momento en el que desee diseñar una coreografía que contenga alguna figura acrobática. El proyecto se desarrolló bajo la metodología de Proceso Unificado Ágil (AUP) adoptando una arquitectura Modelo, Vista, Controlador (MVC) junto al paradigma de programación orientado a objetos (POO). Para su implementación, se utiliza la tecnología del sensor Kinect que ayuda al reconocimiento del esqueleto y el movimiento de los usuarios. Además, se apoyó en el cálculo de ángulos que se forman en algunas partes del cuerpo, empleando el software GeoGebra para el cálculo de ángulos que se forman en algunas partes del cuerpo. Por último, para obtener una evaluación, se creó un algoritmo que extrae coordenadas tridimensionales correspondientes a unas articulaciones especificas del usuario, agrupándose por vectores, buscando con ello el cálculo y la comparación de cada uno de los ángulos formados y así proporcionarle al usuario conocer si la figura acrobática se está realizando de manera correcta.</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Machine learning</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>The project develops a web-based tool for evaluating acrobatic dance techniques, using machine learning to analyze sensor data and provide feedback.</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Herramientas computacionales, Sensor Kinect, Programación orientada a objetos</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>Procesamiento digital de imagenes</t>
@@ -3685,7 +4803,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:14:16+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4030,12 +5152,30 @@
           <t>El CIAT busca contribuir a un auge, potencialmente global, de la yuca a través de un mejoramiento en rendimiento y calidad de producto, mejor agronomía y esfuerzos concertados para combatir plagas y enfermedades emergentes. Es por ello que el área de Genética de Yuca es un motor muy importante en el cumplimiento de la estrategia del CIAT y en particular el laboratorio de Cultivo de Tejido porque es el responsable de conservar los materiales que están en análisis y luego distribuir estos materiales a la misma comunidad CIAT y sus socios para continuar con la investigación en este cultivo. Las operaciones que se realizan en el área de Genética de Yuca y en especial en el laboratorio, en el invernadero y en el campo generan cierta cantidad de datos que para el área es importante almacenar ya que se convertirán en información crítica para tomar decisiones en las investigaciones. Adicionalmente, estas operaciones acarrea ciertos costos que también son de interés para el líder del área. Por otro lado, las plantas que conserva el laboratorio son afectadas por diversos movimientos o procedimientos durante todo su ciclo de vida, y para el área de Genética de Yuca es útil hacer el seguimiento de cada uno de los movimientos o procedimientos que se le efectúan a los genotipos para conocer de manera detallada el proceso de evolución de los mismos. Con base en lo anterior es necesario un sistema para estructurar y configurar los procesos, gestionar los recursos y llevar el registro de los genotipos conservados junto con los procedimientos que se le aplican, que permita llevar la trazabilidad de determinado genotipo y conocer los costos asociados y que además sirva como una herramienta de administración y gerenciamiento.</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+      <c r="H70" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a management system for the CIAT's in vitro plant bank, which involves storing data and tracking costs related to genetic research operations.</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Sistemas de información Web, Banco de plantas in vitro, Genética de Yuca</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -4051,7 +5191,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:14:30+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4075,12 +5219,34 @@
 </t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Data mining</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a system to manage procurement and sales processes for Roger's, an establishment dedicated to fast food production and sales. The system also uses data mining to support decision-making in purchasing ingredients and selling products.</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Sistemas de información, Compras, Administración de ventas, Toma de decisiones, Competitividad</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -4096,7 +5262,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:14:46+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4123,12 +5293,30 @@
           <t>La empresa Nuevos Medios, tiene como producto una plataforma de aprendizaje en línea (elearning) llamada kme Lx (Knowledge Management Environment, Learning Experience) que le permite a sus clientes administrar su ambiente de aprendizaje, olvidando los obstáculos de espacio, tiempo y distancia, brindando la posibilidad de gestionar las capacitaciones e inducciones de sus empleados. De igual forma los cursos para que los estudiantes tengan acceso de manera virtual, haciéndoles un continuo seguimiento desde cualquier dispositivo, sean computador, tablet o smartphone. Debido a que el aprendizaje y el modo en que la persona adquiere conocimientos no tiene una forma definida como normalmente se piensa, la empresa Nuevos Medios con su plataforma de aprendizaje kme Lx, tomó la decisión de expandirse implementando el estándar LTI, (Learning tools interoperability) que permitirá a los administradores y tutores reutilizar contenidos que han creado otras personas, que viven en el ecosistema educativo virtual o e-learning y que está alojado en varios sitios por todo el internet, satisfacer las necesidades de sus usuarios. Si se reúne un conjunto de contenidos, que satisfacen necesidades específicas en un curso de kme Lx. El resultado será un curso con contenidos variados que hará la experiencia de aprendizaje más amena y de alta calidad para el estudiante y para el tutor o administrador. Con este módulo y bajo este estándar LTI, que facilita mucho la comunicación entre plataformas y herramientas externas, la plataforma kme Lx logrará ampliar y obtener una alta calidad en el proceso de formación del estudiante y que ayudará al tutor a crear sus cursos de manera fácil, rápida y económica, debido a que se va a reutilizar y adaptar los recursos disponibles que proveen estas herramientas de aprendizaje. Además de eso, se busca que la plataforma pueda proveer los cursos y contenidos que se han creado nativamente en ella y puedan utilizarse en otros ambientes de aprendizaje que lo requieran.</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+      <c r="H72" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>The project focuses on the implementation of an LTI module in a learning management system, which is clearly an e-learning platform.</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>e-learning, ambientes virtuales de aprendizaje, plataforma de aprendizaje</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -4144,7 +5332,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:14:59+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4253,12 +5445,30 @@
           <t>El proyecto IMEKT CLINIC (International Medical Knowledge Transmission) que se proyecta como una clínica de alta especialidad y centro de capacitación internacional, fundado en 2010 y actualmente en etapa de ejecución, nació como una propuesta enfocada en la difusión del conocimiento médico, específicamente el relacionado con procedimientos quirúrgicos permitiendo a médicos especialistas extranjeros dedicados a la investigación o precursores en algún nuevo procedimiento quirúrgico capacitar a sus homólogos colombianos por medio de congresos, seminarios, procedimientos quirúrgicos didácticos y conferencias. Este proyecto pretende ser un referente en lo que se refiere a la difusión del conocimiento médico. Para sistematizar todos sus procesos, la clínica ha decidido encomendar la tarea de desarrollar un aplicativo a la empresa IPSOFT-SA. En el presente trabajo de grado se aborda el rediseño y desarrollo de algunos módulos pertenecientes al aplicativo con el fin de proveer a la clínica IMEKT una herramienta informática apropiada que facilite su funcionamiento.</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+      <c r="H74" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>The project focuses on developing software modules for managing sales, contacts, and client scheduling for a medical clinic's operations.</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Difusión del conocimiento, Clínica de alta especialidad, Desarrollo de software</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -4274,7 +5484,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:15:12+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4414,12 +5628,30 @@
           <t>El presente proyecto se basó en una problemática que se genera alrededor de la gestión de calificaciones de las instituciones educativas de Colombia, donde no se está evidenciando las falencias que tienen los estudiantes con respecto a los estándares de competencia dadas por el Ministerio de Educación Nacional. Para dar cumplimiento al problema propuesto se realizó el respectivo análisis, diseño y desarrollo de una aplicación web con modernas tecnologías para los procesos de competencia y estándares para determinar el rendimiento académico de los estudiantes, todo esto relacionado con la programación académica de la Institución. En la solución del proyecto , se basó en la metodología ICONIX y el uso de patrones arquitectónicos que plantea el Framework de Laravel, estableciendo un producto de alta calidad que desempeña las funcionalidades requeridas, ofreciendo los módulos más importantes para el planteamiento del problema como la gestión del año lectivo, la gestión académica, gestión de calificaciones y las más primordial la gestión de reportes donde se va evidenciar el rendimiento de cada estudiante por medio de los estándares de competencia</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+      <c r="H77" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a web application for managing educational standards and student performance in Colombian institutions, using modern technologies like Laravel.</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Sistemas de información Web, Competencias en educación, Estándares de Educación, Calificaciones, Rendimiento académico</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -4435,7 +5667,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:15:26+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4597,12 +5833,30 @@
 </t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
+      <c r="H80" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>The project develops a web application for the UMATA unit in Trujillo, which automates processes and supports decision-making for users/beneficiaries. This fits well under enterprise information systems.</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Aplicaciones Web, Bases de datos, Unidad Municipal de Asistencia Técnica Agropecuaria (UMATA), Toma de decisiones</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -4618,7 +5872,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:15:42+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4649,12 +5907,30 @@
           <t>En este proyecto, se hace una investigación acerca de los diferentes modelos emocionales para posteriormente relacionarlos con un modelo basado en el evolutivo tradicional. Todo esto, con el fin de implementar un prototipo que permita realizar simulaciones con Non-Player Character afectados por emociones, en aras de definir su relevancia a la hora de ser utilizadas en entornos de simulación de multitudes. A lo largo de este documento se presentan las distintas fases de su ejecución: Investigación, Implementación, Pruebas y Análisis. Así como los conceptos necesarios para su comprensión y las herramientas utilizadas para alcanzar los objetivos definidos. Por último, debido a la extensión del título proyecto, se hará referencia a sí mismo como el Proyecto SEA; donde SEA son las siglas para Ser Emocional Artificial, un nombre definido por su facilidad de pronunciación, poca extensión y pertinencia con las características y objetivos del proyecto.</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Multi-agent systems</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
+      <c r="H81" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>The project focuses on implementing a prototype for Non-Player Characters (NPCs) that are influenced by emotions, which falls under the domain of multi-agent systems.</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Non-Player Character (NPC), Computación emocional, Vida artificial, Simulación por computador</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr">
         <is>
           <t>Inteligencia arificial</t>
@@ -4670,7 +5946,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:15:57+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4700,12 +5980,30 @@
           <t>La usabilidad de los sistemas interactivos es un atributo de calidad del software que posibilita a los usuarios realizar las tareas de forma fácil, intuitiva y cómoda, permitiendo alcanzar sus objetivos de manera rápida y satisfactoria. Paralelamente, la ausencia de herramientas para apoyar la evaluación de la usabilidad, específicamente evaluaciones heurísticas, se traduce en una desventaja para los evaluadores a la hora de llevar a cabo la verificación del grado de conformidad de un software en cuanto a un atributo importante como la usabilidad, así pues, la ausencia de dichas herramientas repercute en el tiempo empleado en la ejecución de la evaluación y a prescindir de aspectos importantes a la hora de analizar y realizar la respectiva conclusión. Con base en lo anterior, el aplicativo web expuesto en el presente documento se desarrolló en el marco de una investigación aplicada, la cual posibilitó por medio de la metodología de desarrollo Kanban, ofrecer a la comunidad una aplicación web que sirve de apoyo en el proceso de evaluación heurística, permitiendo a los evaluadores facilitar el proceso de análisis de los resultados y contribuir con trasmisión de conocimiento de manera oportuna.</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
+      <c r="H82" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a web application to support heuristic evaluations of usability for interactive systems.</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Usabilidad, Evaluación heurística, Aplicaciones Web, Sistemas de información</t>
+        </is>
+      </c>
       <c r="K82" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -4721,7 +6019,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:16:09+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4754,12 +6056,34 @@
           <t>En este trabajo de grado se diseña, modela e implementa una aplicación para dispositivos móviles Android, mediante el empleo de técnicas de inteligencia artificial y características especiales que presentan esta clase de artefactos, con el fin de utilizarlos como herramientas de soporte útiles en las actividades diarias de los ciclistas. La aplicación en principio funciona en base a un sistema de recomendación, el cual utiliza los datos compartidos diariamente entre cada persona y su teléfono personal con el fin de generar información relevante y de gran ayuda para la persona en actividades relacionas con el uso de la bicicleta. Mediante el uso de un servicio web se mantiene la aplicación en sincronización constante con los datos de todos los usuarios, permitiendo determinar la información más relevante para determinado grupo de personas en base a un estudio de características comunes. Finalmente, con el desarrollo de la aplicación se busca fomentar el uso de la bicicleta como medio de transporte, deporte y recreación, sacando provecho de sus dispositivos móviles y las ventajas que estos ofrecen en el desarrollo de la vida diaria.</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Recommender systems</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Mobile applications</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>The project focuses on designing a mobile application for Android devices that uses recommendation techniques to support cyclists' training and competition processes.</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Aplicaciones móviles, Sistemas de recomendación Web, Ciclistas</t>
+        </is>
+      </c>
       <c r="K83" t="inlineStr">
         <is>
           <t>Sistemas de recomendación</t>
@@ -4775,7 +6099,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:16:21+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4803,12 +6131,34 @@
           <t>En este proyecto se diseñó e implementó una aplicación web basada en la arquitectura (SOA). Una arquitectura que junto a la metodología de desarrollo SOMA, un hibrido entre la metodología RUP[13] y un enfoque basado en modelo de negocios, exigió un análisis tanto de los requerimientos de la aplicación, como del modelo de negocio de la fundación IPS FIME. En el análisis del modelo de negocio se identificaron políticas de la organización claves para establecer el alcance del proyecto y también, se clasificaron actividades en procesos de negocio con el fin de detectar los servicios a implementar. El siguiente paso, fue diseñar los servicios de acuerdo a los objetivos de la empresa, es decir a su modelo de negocio y políticas internas apoyándose en casos de usos y diagramas de Modelos y Notación de Procesos de Negocio (BPMN). Por otra parte, en la implementación se tomó como base la tecnología REST [12], una alternativa a SOAP [14] recomendado por W3C para aplicaciones robustas, la cual establece criterios para la comunicación entre servicios web empleando el protocolo HTTP. Una vez implementados los servicios en módulos de usuarios, pacientes, proveedores e historias clínicas, se integraron cada uno de estos módulos en una aplicación web desarrollada haciendo uso del framework Java Server Faces (JSF), el servidor de aplicaciones web GlassFish V4.0, el gestor de base de datos MySQL y la biblioteca de componentes PrimeFaces.</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a web-based management system for users, patients, providers, and clinical records at FIME, which aligns with the definition of an enterprise information system.</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Arquitectura Orientada a Servicios (SOA), Sistemas de información Web, Administración de bases de datos</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -4824,7 +6174,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:16:37+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5040,12 +6394,30 @@
           <t>Este trabajo de grado se encuentra en el marco de un proyecto denominado Playtherapy que es liderado por el grupo de investigación en Multimedia y Visión por Computador de la Universidad del Valle en colaboración de la Unidad de Medicina Física y Rehabilitación del Hospital Universitario del Valle. El objetivo principal consiste en aumentar la motivación de los pacientes que se encuentran en proceso de rehabilitación física a través de herramientas interactivas. Por ello, se desarrolló un minijuego que se denominó "Fútbol Libre". Por un lado, contribuyendo de este modo al aumento de la oferta de minijuegos y por otro lado, como fuente de goce y entretenimiento y que el usuario olvide que se encuentra en un ambiente clínico. Este juego, incluye los movimientos de flexión y extensión de cadera y rodilla. Estos movimientos son detectados a través del sensor Kinect 2.0. También, se tiene como aporte la realización de una guía de estilo y el uso de un instrumento de medida que permita valorar el grado de la experiencia del jugador (PX) del videojuego en base a la Jugabilidad dentro de un sistema interactivo. Para el desarrollo, se utilizaron dos metodologías: Game Scrum para el desarrollo de videojuegos y el Modelo de Proceso de la Ingeniería de la usabilidad y de la accessibilidad como estrategia para implementar la Usabilidad y Jugabilidad como valor agregado al sistema interactivo. Finalmente, se logró concluir que una propuesta de videojuegos serios dentro de un contexto como la terapia de rehabilitación física, tiene buena aceptación por parte de los usuarios finales, ya que las pruebas y la interacción con los pacientes y terapeutas así lo demostró.</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Serious games</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
+      <c r="H88" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>The project develops a video game aimed at supporting physical therapy for adult patients, focusing on rehabilitation and patient motivation through interactive tools.</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Videojuegos, Terapia física, Rehabilitación física, Usabilidad, Evaluación heurística</t>
+        </is>
+      </c>
       <c r="K88" t="inlineStr">
         <is>
           <t>Juegos serios</t>
@@ -5061,7 +6433,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:16:51+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5091,12 +6467,34 @@
           <t>El diagnóstico oportuno de una enfermedad es un proceso crítico, debido a que hay enfermedades de alto riesgo en las cuales un temprano diagnóstico es fundamental para evitar consecuencias irreversibles. Nuestro trabajo se enfoca en diseñar y probar estrategias para la categorización de la retinopatía diabética, a partir de información de imágenes procesadas de fondo de ojo con su respectivo diagnóstico. Esta enfermedad debe ser detectada en una etapa temprana, ya que de lo contrario el paciente presentará pérdida parcial o total de la visión, proceso gradual e irreversible. En diferentes estudios realizados se indica que el diagnóstico de un médico se ve afectado positivamente al estar apoyado de un sistema de decisión, lo que conlleva a una disminución de los exámenes realizados y así disminución de tiempo de espera. Para realizar la categorización de esta enfermedad, se utilizaron datos de imágenes de fondo de ojo procesadas, proporcionados por la base de datos Messidor y el proyecto An ensemble-based system for automatic screening of diabetic retinopathy . Así mismo, se realizó una exhaustiva revisión de literatura sobre algoritmos que se utilizan para el diagnóstico de la enfermedad, encontrando que los más relevantes son: Redes neuronales y Máquinas de Soporte Vectorial. Posteriormente, se llevó a cabo la implementación de tres algoritmos de inteligencia artificial para el diagnóstico de la enfermedad: Redes neuronales entrenadas con Backpropagation, Redes neuronales evolutivas y Máquina de soporte Vectorial. Al realizar un análisis comparativo de estos algoritmos, se encuentra que las redes neuronales entrenadas con Backpropagation son las que presentan mejores resultados en términos de precisión y tiempo de ejecución.</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Computer vision</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Machine learning</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>The project focuses on the categorization of diabetic retinopathy using image processing techniques and machine-learning algorithms, making 'Computer vision' the primary term with 'Machine learning' as a secondary contribution.</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial, Algoritmos genéticos, Máquina de soporte vectorial, Redes neuronales, Retinopatía</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr">
         <is>
           <t>Inteligencia arificial</t>
@@ -5112,7 +6510,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:17:08+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5140,12 +6542,30 @@
           <t>Este trabajo de grado forma parte de un proyecto denominado EnglishPlay, el cual consiste en el desarrollo de un videojuego como herramienta en el proceso de enseñanza del idioma inglés para los estudiantes de la asignatura Lectura de Textos Académicos en Inglés I de la Universidad del Valle. El aporte en el desarrollo de EnglishPlay consistió en el desarrollo de dos minijuegos (también denominados desafíos), éstos fueron Camino Corrrecto y Láser. Además de los desafíos se desarrolló el mundo castillo, el cual es considerado como un nivel dentro del juego, éste combina el entretenimiento (enemigos, trampas, ambientaicón, sonidos, efectos) y el aprendizaje mediante los minijuegos (son 8 minijuegos implementados en el mundo que se desarrolló, pero sólo dos fueron de este trabajo, y los otros 6 fueron desarrollados por los compañeros del equipo de desarrollo de EnglishPlay). Cada mundo tiene temas diferentes de la asignatura; además del aporte en el videojuego, se desarrolló también un módulo web en donde los estudiantes pueden realizar tests, los cuales sirve para revisar el desempeño del estudiante. El mundo castillo contiene como aprendizaje del inglés, los temas de los adjetivos, comparativos y superlativos. Para apoyar el proceso de enseñanza de la asignatura y aumentar la motivación de los estudiantes por aprender, se ofrece mediante ésta herramienta, una alternativa diferente de aprendizaje, más interactiva, práctica y a la vez divertida, que logran crear un ambiente diferente al del aula, al olvidarse de los roles profesor-estudiante. Para ello los minijuegos tienen diferentes metodologías de aprendizaje; en el desafío de Camino Correcto son ejercicios de traducción de frases del inglés al español, y en el desafío Láser se trata de recorrer un laberinto y contestar correctamente una pregunta con múltiples respuestas. Un aporte más en las metodologías de enseñanza, fue la realización del Libro de la Sabiduría, el cual es una fuente de información sobre los temas que se enseñan dentro del juego, es una especie de enciclopedia, la cual contiene la explicación textual del tema que el estudiante desee consultar, e imágenes a modo de ejemplo, de tal manera que el estudiante pueda asimilar la información más fácilmente.</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Serious games</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
+      <c r="H90" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>The project develops a video game with mini-games to support English language teaching for engineering students, focusing on interactive and engaging learning methods.</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Videojuegos, Minijuegos, Enseñanza del inglés</t>
+        </is>
+      </c>
       <c r="K90" t="inlineStr">
         <is>
           <t>Juegos serios</t>
@@ -5161,7 +6581,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:17:21+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5622,12 +7046,30 @@
           <t>En este trabajo de grado se aborda la problemática que se presenta en la Universidad del Valle sede Tuluá en cuanto las bajas calificaciones en la asignatura Lectura de Texto Académicos en Inglés I que cursan los estudiantes de primer semestre en Ingeniería de Sistemas; los aportes de este trabajo de grado al proyecto de EnglishPlay fue un minijuego llamado plataformas, el desarrollo del mundo bosque en el videojuego y un módulo web que registra el avance en el juego de cada estudiante, entre otras tareas. El videojuego se desarrolló bajo la metodología ágil Game-Scrum. Se utilizó un modelo de tres capas para el desarrollo del módulo. El fin con el que se desarrolló este proyecto es para apoyar el proceso de enseñanza y aprendizaje del idioma inglés haciendo uso de un videojuego. En EnglishPlay existe un mundo llamado Bosque el cual contiene dos temáticas de la asignatura Lectura de Textos Académicos en Inglés I tiempos perfectos y voz pasiva, la manera de presentar a los estudiantes dichos temas es por medio de desafíos, los cuales son 8 y están presentes en este mundo, estos ofrecen diferentes metodologías de enseñanza. Además, el videojuego también le ofrece al estudiante retos como el recorrer un escenario recolectando objetos, derrotando enemigos, superando obstáculos, entre otras acciones. El módulo web tiene como finalidad mostrar al usuario su avance en el videojuego para que este pueda observar qué personaje tiene seleccionado y qué características posee este, también le permite ver qué porcentaje del juego ha desbloqueado y el puntaje que obtuvo en cada desafío que jugó.</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Serious games</t>
+        </is>
+      </c>
       <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
+      <c r="H98" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a video game to support English academic reading skills, which aligns with the definition of serious games as educational videogames.</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Videojuegos, Minijuegos, Estrategias de apoyo, Herramientas didácticas</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr">
         <is>
           <t>Juegos serios</t>
@@ -5643,7 +7085,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>2026-04-26T15:17:42+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -11270,12 +12716,30 @@
           <t>El proyecto consta en la realizaci´on de un prototipo de videojuego y un algoritmo emocional el cual estar´a encargado de detectar la emoci´on del jugador al finalizar cada nivel y a ra´ız de este resultado ajustar´a la dificultad de las preguntas a realizarse en cada nivel presentado. Alo largo del documento se ir´a presentando toda la informaci´on recopilada acerca del proceso de creaci´on del clasificador emocional al igual que todo el proceso que se realiz´o para el dise˜no y programaci´on del prototipo de videojuego, por ´ultimo se mostrar´an los resultados de las pruebas de aceptaci´on y usabilidad realizadas en la instituci´on educativa</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Serious games</t>
+        </is>
+      </c>
       <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
+      <c r="H183" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a video game prototype to enhance English language skills in fifth-grade children, incorporating emotional computing techniques.</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>videojuegos, algoritmos emocionales, computación emocional</t>
+        </is>
+      </c>
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
@@ -11287,7 +12751,11 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N183" t="inlineStr"/>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:40:13+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -11358,7 +12826,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2025S01</t>
+          <t>2024S01</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11424,7 +12892,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2025S02</t>
+          <t>2024S02</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11442,12 +12910,30 @@
           <t>Cada vez m´as, las emisiones descontroladas de gases est´an elevando la tempera tura de nuestro planeta y cambiando las temporadas de lluvia. Esto tiene efectos profundos, como la disminuci´on de los glaciares, un aumento en la frecuencia de eventos clim´aticos extremos, modificaciones en los patrones clim´aticos estacionales, entre otros. El r´apido cambio clim´atico, en combinaci´on con el crecimiento de la poblaci´on y los ingresos a nivel mundial, plantea una amenaza significativa para la seguridad alimentaria en todo el mundo. La agricultura es particularmente vulnerable a estos cambios en el clima. El incre mento de las temperaturas reduce la producci´on de cultivos esenciales y fomenta la propagaci´on de especies invasoras y plagas. Las alteraciones en los patrones de lluvias aumentan el riesgo de cosechas fallidas a corto plazo y reducen la producci´on a largo plazo. Con el fin de identificar ´areas id´oneas para cultivos de importancia econ´omica en Roldanillo- Valle del Cauca se hizo uso de t´ecnicas de Machine Learning como Random Forest, esto a partir del uso del lenguaje de programaci´on de R apoyado en los Sistemas de Informaci´on Geogr´afico y fuentes de datos clim´aticas hist´oricas (1990- 2020) y futuras (2040-2069), estas ´ultimas con bases en proyecciones de cambio clim´atico. Los resultados de este estudio proporcionaron informaci´on valiosa sobre las ´areas que ser´ıan adecuadas para la agricultura en el futuro, teniendo en cuenta los cam bios clim´aticos proyectados. Este enfoque combina datos bioclim´aticos, t´ecnicas de desescalado y aprendizaje autom´atico implementado en R para ofrecer una visi´on predictiva de la aptitud agr´ıcola en el tiempo, lo que puede ser de gran utilidad para la planificaci´on y toma de decisiones en la agricultura y la seguridad alimentaria a largo plazo</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Machine learning</t>
+        </is>
+      </c>
       <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
+      <c r="H186" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>The project primarily uses the Random Forest algorithm for machine learning to evaluate suitable areas for crops under climate change conditions, supported by GIS techniques.</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Agricultura, Random forest, Sistema de Información Geográfica, cambio climático</t>
+        </is>
+      </c>
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr">
         <is>
@@ -11459,12 +12945,16 @@
           <t>qwen2.5:14b-instruct</t>
         </is>
       </c>
-      <c r="N186" t="inlineStr"/>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:42:04+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2025S03</t>
+          <t>2024S03</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11526,7 +13016,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2025S04</t>
+          <t>2024S04</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11589,7 +13079,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2025S05</t>
+          <t>2024S05</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11655,7 +13145,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2025S06</t>
+          <t>2024S06</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11721,7 +13211,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2025S07</t>
+          <t>2024S07</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -11784,7 +13274,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2025S08</t>
+          <t>2024S08</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -11847,7 +13337,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2025S09</t>
+          <t>2024S09</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -11910,7 +13400,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2025S10</t>
+          <t>2024S10</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -11972,7 +13462,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2025S11</t>
+          <t>2024S11</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12038,7 +13528,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2025S12</t>
+          <t>2024S12</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12100,7 +13590,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2025S13</t>
+          <t>2024S13</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12165,7 +13655,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2025S14</t>
+          <t>2024S14</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12231,7 +13721,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2025S15</t>
+          <t>2024S15</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12294,7 +13784,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2025S16</t>
+          <t>2024S16</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12360,7 +13850,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2025S17</t>
+          <t>2024S17</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12426,7 +13916,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2025S18</t>
+          <t>2024S18</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12489,7 +13979,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2025S19</t>
+          <t>2024S19</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12555,7 +14045,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2025S20</t>
+          <t>2024S20</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12617,7 +14107,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2025S21</t>
+          <t>2024S21</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12679,7 +14169,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2025S22</t>
+          <t>2024S22</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12746,7 +14236,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2025S23</t>
+          <t>2024S23</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12810,7 +14300,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2025S24</t>
+          <t>2024S24</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12873,7 +14363,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2025S25</t>
+          <t>2024S25</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12939,7 +14429,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2025S26</t>
+          <t>2024S26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13003,7 +14493,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2025S27</t>
+          <t>2024S27</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13067,7 +14557,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2025S28</t>
+          <t>2024S28</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13130,7 +14620,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2025S29</t>
+          <t>2024S29</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13194,7 +14684,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2025S30</t>
+          <t>2024S30</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13260,7 +14750,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2025S31</t>
+          <t>2024S31</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13322,7 +14812,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2025S32</t>
+          <t>2024S32</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13384,7 +14874,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2025S33</t>
+          <t>2024S33</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13446,7 +14936,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2025S34</t>
+          <t>2024S34</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13511,7 +15001,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2025S35</t>
+          <t>2024S35</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13573,7 +15063,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2025S36</t>
+          <t>2024S36</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13639,7 +15129,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2025S37</t>
+          <t>2024S37</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13701,7 +15191,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2025S38</t>
+          <t>2024S38</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13764,7 +15254,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2025S39</t>
+          <t>2024S39</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -13826,7 +15316,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2025S40</t>
+          <t>2024S40</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -13888,7 +15378,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2025S41</t>
+          <t>2024S41</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -13950,7 +15440,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2025S42</t>
+          <t>2024S42</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14016,7 +15506,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2025S43</t>
+          <t>2024S43</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14092,7 +15582,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2025S44</t>
+          <t>2024S44</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14148,6 +15638,1340 @@
       <c r="N228" t="inlineStr">
         <is>
           <t>2026-04-25T17:31:19+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2025S01</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>SISTEMA DE IDENTIFICACION DE INSTRUMENTOS MUSICALES DE LA REGION ANDINA USANDO TECNICAS DE MACHINE LEARNING</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Identificador, Intrumentos musicales, Musica andina, Inteligencia Artificial, Machine Learning</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Este proyecto presenta el desarrollo de un sistema de identificación de instrumentos musicales específicos de la región andina utilizando diferentes técnicas de Machine Learning. El sistema propuesto emplea algoritmos de clasificación para analizar y categorizar sonidos musicales, facilitando la identificación automática de instrumentos como la quena, el charango, la zampoña y el bombo andino, entre otros adicionales. Se recolectarán datos acústicos de diversas fuentes y se procesarán para extraer características relevantes que alimenten los modelos de aprendizaje automático.</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Machine learning</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a system to identify Andean musical instruments using machine learning techniques, with the central contribution being the classification algorithms and models.</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>Identificador, Intrumentos musicales, Musica andina, Machine Learning</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>qwen2.5:14b-instruct</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:29:06+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2025S02</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>PROTOTIPO DE SISTEMA EN GESTION INTEGRAL DE FACTURACIÓN DIGITAL PARA PEQUENOS PRESTADORES DE SERVICIOS PÚBLICOS</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Sistema de facturación, Servicios públicos, Prototipo wireframes, Prototipo mockups</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Este documento describe la implementación de un sistema de facturación digital para pequeños prestadores de servicios públicos, específicamente en el contexto de acueductos de pequeña escala. La necesidad de optimizar y automatizar este proceso se debe a las limitaciones y deficiencias actuales en la gestión financiera de estos sistemas, que afectan la precisión, eficiencia y transparencia en la administración de los mismos. El objetivo del prototipo logrado es proporcionar un sistema de facturación digital adaptado a las particularidades y necesidades específicas de las pequeñas entidades que prestan servicios públicos. El prototipo proporciona funcionalidades clave para agilizar la generación de facturas, facilitar la gestión de usuarios y mejorar la transparencia en la administración financiera, permitiendo obtener datos específicos que pue den servir como base de datos informativa para la entidad. La creación del prototipo se realizó mediante un enfoque ágil, utilizando instrumentos y tecnologías actuales para el diseño y desarrollo del sistema. Se desarrollaron wireframes y mockups que permitieron dar una percepción clara del sistema al usuario final. El prototipo fue sometido a pruebas que confirmaron su funcionalidad y eficiencia en el procesamiento de datos y carga masiva de información. Los resultados obtenidos muestran que el prototipo tiene una buena aceptación y su procesamiento es eficiente. Se espera que el sistema desarrollado contribuya significativamente a la mejora de la gestión financiera en pequeños acueductos, ofreciendo una solución integral y adaptada a las necesidades de la entidad que lo desee implementar. La implementación de este sistema puede tener un impacto positivo en la eficiencia y transparencia de la gestión financiera de estos sistemas.</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a digital billing system for small public service providers, which falls under enterprise information systems.</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>Sistema de facturación, Servicios públicos, Prototipo wireframes</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>qwen2.5:14b-instruct</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:29:18+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2025S03</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>SISTEMATIZACIÓN DE LA GESTIÓN ADMINISTRATIVA DE INFORMACIÓN Y LÓGICA DE NEGOCIO PARA LA RECOLECCIÓN DE DESECHOS EN LA EMPRESA AGUAS DE LA SABANA</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Desarrollo de software, sistematización, gestión administrativa, operación de negocios</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>En este documento se aborda la profundización respecto a la necesidad de un sistema integral alrededor del gestionamiento y la administración de la información de las operaciones de negocio en la empresa Aguas de la Sabana de Bogotá S.A E.S.P., una empresa privada prestadora de los servicios de acueducto, alcantarillado y aseo, que contribuye al desarrollo de los municipios de Cota, Funza y Tenjo. El objetivo es mejorar la administración de acuerdos y tarifas según norma CRA 151 del 2001, Anexo 8, la gestión de clientes y técnicos/operarios registrados, la relación de información de rutas, micro rutas y clientes correspondientes a las mismas, y la gestión de los recursos operacionales como los camiones de recolección, entre otros. Contribuyendo así a la mejora de la experiencia tanto del administrador como de los operarios y al cumplimiento normativo de la empresa.</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a system for managing administrative and business operations in the waste collection sector of Aguas de la Sabana, including customer management, resource allocation, and compliance with regulatory standards.</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>Desarrollo de software, gestión administrativa, operación de negocios</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>qwen2.5:14b-instruct</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:29:31+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2025S04</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>DESARROLLO DE UN PROTOTIPO DE SISTEMA DE RECOMENDACIÓN PARA ELECCIÓN DE VEHÍCULO TIPO MOTOCICLETA BASADO EN FILTRADO COLABORATIVO</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Inteligencia Artificial, Sistemas de recomendación, Filtrado Colaborativo, Características específicas, Motocicletas</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>La elección de una motocicleta es un proceso complejo que puede resultar abrumador para los usuarios debido a la diversidad de opciones disponibles y las diferentes necesidades y preferencias individuales. La propuesta de un sistema de recomendación de motocicletas buscó abordar este desafío al proporcionar orientación personalizada y precisa a los usuarios en su búsqueda del vehículo perfecto. Este sistema se implementó utilizando una metodología basada en el análisis de datos, el aprendizaje automático y el filtrado colaborativo. A través de estas tecnologías, se comprendieron las preferencias de los usuarios y se sugirieron motocicletas que se adaptaran mejor a sus necesidades y gustos individuales. De esta manera, el sistema ofreció recomendaciones personalizadas que se alinearon específicamente con las características y preferencias únicas de cada usuario, mejorando significativamente la precisión y relevancia de las sugerencias. Los resultados obtenidos mostraron una mejora considerable en la satisfacción del usuario al reducir el tiempo y esfuerzo necesarios para encontrar una motocicleta adecuada, adaptándose de forma precisa a las necesidades personales de cada individuo.</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Recommender systems</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a recommendation system for motorcycle selection based on collaborative filtering, which is clearly stated in the title and abstract.</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>Sistemas de recomendación, Filtrado Colaborativo, Inteligencia Artificial</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>qwen2.5:14b-instruct</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:29:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2025S05</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>PRONUNCIAPP: PROTOTIPO DE APLICACION WEB PARA LA MEJORA DE LA PRONUNCIACIÓN DEL INGLÉS EN LOS ESTUDIANTES DE LA CARRERA DE INGENIERÍA DE SISTEMAS DE LA UNIVERSIDAD DEL VALLE, SEDE TULUÁ</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Prototipo aplicación web, inteligencia artificial, idioma ingles, PronunciApp</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>PronunciApp es un prototipo de aplicación web desarrollado como proyecto de grado para proporcionar una mejora sobre la pronunciación del idioma inglés a estudiantes de Ingeniería de Sistemas de la Universidad del Valle, sede Tuluá. El sistema implementado permite a los usuarios grabar su voz al repetir palabras en inglés, las cuales son analizadas utilizando tecnologías de reconocimiento de voz para generar retroalimentación sobre aspectos de la pronunciación. La aplicación se desarrolló utilizando Angular 19 para la interfaz de usuario, FastAPI para el backend, y se desplegó en la plataforma Azure. El proceso de desarrollo siguió la metodología Scrumban a lo largo de 40 sprints, aplicando principios de diseño UX/UI para crear una herramienta que permite la práctica de pronunciación mediante el análisis de grabaciones de audio.</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Artificial intelligence</t>
+        </is>
+      </c>
+      <c r="H233" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a web application called PronunciApp that uses AI technologies for voice recognition to provide feedback on English pronunciation.</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>Prototipo aplicación web, inteligencia artificial, idioma ingles, PronunciApp</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>qwen2.5:14b-instruct</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:29:55+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2025S06</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>CREACIÓN DE MÓDULOS INTERACTIVOS PARA EL DESARROLLO CONTINUO DE LA ORATORIA Y EL PENSAMIENTO CRÍTICO DE TEXTOS EN EL PROTOTIPO DE ENSEÑANZA DE HABILIDADES BLANDAS</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Procesamiento del lenguaje natural, Comunicación efectiva, pensamiento crítico, plataforma educativa, habilidades blandas, inteligencia artificial.</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Con frecuencia, se observa que la importancia de ciertas habilidades es pasada por alto en los programas de formación, a pesar de su relevancia en el mercado laboral actual y futuro. La comunicación efectiva y el pensamiento crítico constituyen pilares importantes para que los ingenieros puedan abordar los desafíos venideros y ofrecer soluciones de calidad a sus clientes. El descuido de estas habilidades en la formación de ingenieros puede ocasionar consecuencias negativas tanto en su desempeño profesional como en el éxito de los proyectos que emprendan. Este proyecto se centró en crear y poner en marcha módulos interactivos para el desarrollo de habilidades de oratoria y pensamiento crítico dirigidos específicamente a los estudiantes de ingeniería de sistemas de la Universidad del Valle en Tuluá. Se implementaron estrategias educativas que incluyen el uso de inteligencia artificial y procesamiento de lenguaje natural para proporcionar retroalimentación personalizada a los estudiantes. Al impulsar el desarrollo de estas habilidades, las instituciones educativas pudieron contribuir de manera significativa a la formación de profesionales versátiles y capacitados que estuvieran mejor preparados para enfrentar los desafíos venideros con mayor confianza y competencia.</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Natural language processing</t>
+        </is>
+      </c>
+      <c r="H234" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>The project focuses on developing interactive modules for soft skills education using AI and NLP to provide personalized feedback, fitting the E-learning category with a secondary focus on Natural Language Processing.</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>Procesamiento del lenguaje natural, plataforma educativa, inteligencia artificial, pensamiento crítico, habilidades blandas</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>qwen2.5:14b-instruct</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:30:11+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2025S07</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>DESARROLLO DE UN SOFTWARE PARA LA PREDICCIÓN DE VENTAS FUTURAS UTILIZANDO MODELOS PREDICTIVOS.</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Aplicativo web, pronostico en ventas, futuras, modelos predictivos, inteligencia artificial, PYMES</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>En este trabajo de grado se aborda el desarrollo de un aplicativo de software para el pronóstico de ventas utilizando algoritmos de inteligencia artificial. El problema evidenciado es la carencia de una herramienta que permita a las pequeñas y medianas empresas (PYMES) tomar mejores decisiones de manera informada para la gestión de su inventario ya que para una empresa tener una buena gestión del inventario es crucial ya que las ventas pueden fluctuar de una manera poco predecible lo que puede llevar a pérdidas eco nómicas por tener poco o demasiado inventario. Las pequeñas empresas, pueden enfrentar más dificultades en la gestión del inventario, lo cual puede resultar poco eficiente debido a que suelen realizar esta gestión de manera manual y sin un estudio previo. El objetivo principal de este trabajo de grado es crear una herramienta capaz de generar pronósticos de ventas precisos a partir de datos históricos, integrando modelos predicti vos entrenados con técnicas de machine learning. Para ello, se implementaron y evaluaron tres modelos distintos: una red neuronal LSTM (Long Short-Term Memory), un modelo de soporte vectorial para regresión (SVM) con distintos kernels, y un modelo estadístico SARIMA (Seasonal Autoregressive Integrated Moving Average). Las métricas utilizadas para evaluar el desempeño de los modelos fueron el Error Cuadrático Medio (MSE), el Error Absoluto Medio (MAE) y el Error Porcentual Absoluto Medio (MAPE). El proyecto fue desarrollado bajo la metodología ágil Scrum, adaptada para un entorno de trabajo individual</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Machine learning</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
+      <c r="H235" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a web application that uses machine learning models to predict future sales for small and medium-sized enterprises.</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>Aplicativo web, pronostico en ventas, modelos predictivos, inteligencia artificial, PYMES</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>qwen2.5:14b-instruct</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:30:24+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2025S08</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>PROTOTIPO DE APLICACIÓN WEB COMO HERRAMIENTA DE APOYO PARA LA EVALUACIÓN DE COMPETENCIAS EN PENSAMIENTO COMPUTACIONAL</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Metodologías educativas, pensamiento computacional, evaluación de competencias, aplicación web</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>El pensamiento computacional se ha consolidado como una habilidad fundamental para el siglo XXI, ya que permite a los individuos comprender y participar activamente en el mundo digital. En el caso de los jóvenes, su desarrollo aporta beneficios significativos en múltiples dimensiones. En primer lugar, promueve el razonamiento lógico y el pensamiento crítico, al requerir que los estudiantes aborden problemas de manera sistemática y estructurada, estas habilidades resultan clave tanto para el desempeño académico como para la toma de decisiones en la vida cotidiana. Además, estimula la creatividad y la innovación, al incentivar la búsqueda de soluciones originales a diversos retos, capacidades especialmente valoradas en el contexto actual. Asimismo, el pensamiento computacional prepara a los jóvenes para enfrentar los desafíos del mercado laboral, especialmente en áreas relacionadas con la ciencia, la tecnología, la ingeniería y las matemáticas, donde estas competencias son cada vez más demandadas. Reconociendo su relevancia, se han propuesto múltiples metodologías para enseñar pensamiento computacional, cada una con distintos enfoques y estrategias de evaluación. Sin embargo, las investigaciones evidencian deficiencias en los métodos de evaluación existentes, lo que dificulta validar de forma efectiva el aprendizaje de estas competencias. Ante esta problemática, el presente trabajo propone el desarrollo de una aplicación web parametrizable, orientada a evaluar las competencias en pensamiento computacional de estudiantes de educación secundaria. La solución se fundamentará en un modelo de evaluación integral que combine enfoques formales e informales, haciendo uso de rúbricas para valorar el desempeño de los estudiantes en tareas específicas relacionadas con el pensamiento computacional.</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a web application to evaluate computational thinking competencies in students, which aligns with the 'Web applications' term.</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>Metodologías educativas, pensamiento computacional, evaluación de competencias, aplicación web</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>qwen2.5:14b-instruct</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:30:37+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2025S09</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>DESARROLLO DE PRUEBAS UNITARIAS PARA EL COMPONENTE FRONT-END DEL SOFTWARE ACADEMIAPP PARA LA EMPRESA WEBCLOSTER SAS</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Desarrollo de software Scrum, pruebas unitarias, gestión acádemica, gestión administrativa, AcademiApp</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Cada vez es más crucial para las universidades sistematizar la gestión tanto administrativa como académica. Varias compañías de software han identificado esta necesidad y han entrado en este mercado, entre ellas Webcloster S.A.S. Webcloster S.A.S. es una empresa que se dedica al desarrollo de software que simplifica la dirección y administración de operaciones tanto empresariales como personales, y ha decidido crear un programa llamado AcademiApp para la gestión académica y administrativa. Este programa consiste en una aplicación en línea que facilita la administración de datos, la consulta de horarios disponibles de las aulas, la evaluación de desempeños, entre otras funciones. Para este proyecto se empleará una metodología de investigación aplicada y, adicionalmente, se utilizará la metodología ágil Scrum. Con lo mencionado anteriormente, se espera desarrollar pruebas y realizar el mantenimiento de los módulos asignados para AcademiApp.</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Software engineering</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>The project focuses on developing unit tests for the front-end component of a software application, which falls under software engineering practices.</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>Desarrollo de software, pruebas unitarias, Scrum</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>qwen2.5:14b-instruct</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:30:48+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2025S10</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>PROTOTIPO WEB COMO SOPORTE PARA LA ENSEÑANZA DE INGLÉS A TRAVÉS DE LA GAMIFICACIÓN Y ALGORITMOS DE PROCESAMIENTO DEL LENGUAJE NATURAL</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Lenguaje natural, gamificación, aprendizaje, habla en ingles, inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>El presente proyecto desarrolló un prototipo web diseñado para mejorar la habilidad del habla en inglés mediante el uso de técnicas de Procesamiento del Lenguaje Natural (PLN) y gamificación. Se aborda la creciente necesidad de herramientas educativas efectivas que involucren a los estudiantes de manera activa y atractiva. El sistema proporciona ejercicios interactivos y elementos de gamificación para motivar a los usuarios a practicar y mejorar su comprensión al momento de hablar en inglés. El enfoque que tiene el sistema aporta al estudiante una herramienta con IA centralizada en distintos algoritmos de PLN con el fin de que el estudiante obtenga un apoyo en el proceso de aprendizaje y que, con ayuda de estos modelos matemáticos, pueda mejorar su fluidez al momento de comunicarse en inglés.</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Gamification</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Natural language processing</t>
+        </is>
+      </c>
+      <c r="H238" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>The project focuses on a web prototype that uses gamification techniques and natural language processing algorithms to support English language learning.</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>gamificación, lenguaje natural, aprendizaje, habla en ingles, inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>qwen2.5:14b-instruct</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:31:00+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2025S11</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>PROTOTIPO DE SOFTWARE WEB PARA EL ANÁLISIS Y EVALUACIÓN DE LA EXPOSICIÓN DE DATOS SENSIBLES Y NO SENSIBLES EN LA RED SOCIAL INSTAGRAM APLICADA EN LA UNIVERSIDAD DEL VALLE SEDE TULUÁ</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Procesamiento de Lenguaje Natural, Web Scraping, campus universitario, privacidad de datos, redes sociales.</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>En esta propuesta de trabajo de grado se busca la implementación de un prototipo de software web para capturar la información de texto de las redes sociales (web Scraping o API web scraper) y poder identificar el nivel de exposición de los datos personales sensibles y no sensibles en los campus universitarios, con este proyecto, se quiere motivar a otras entidades educativas a adoptar un enfoque similar, donde el factor clave es promover una cultura ge neral de privacidad y seguridad en línea en todas las comunidades universitarias. Asimismo, se espera formar un futuro digital donde la protección de datos personales sea uno de los pi lares fundamentales, garantizando así un mejor ambiente universitario tanto confiable como respetuoso para todos los miembros que la componen. El presente proyecto constituye una posibilidad hacia la creación de entornos universita rios más seguros y respetuosos de la privacidad. Destacando el papel crucial que la tecnología desempeña como aliada en la protección de los derechos individuales y colectivos, con la aspiración a transformar no solo el entorno académico universitario, sino también a que sirva como ejemplo para otras instituciones educativas en Colombia. El trabajo pretende usar para su desarrollo, las técnicas de procesamiento de lenguaje natural y las tecnologías de trata miento de datos teniendo en cuenta la normatividad de la privacidad de datos.</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Natural language processing</t>
+        </is>
+      </c>
+      <c r="H239" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a web-based tool to analyze and evaluate data exposure in Instagram, using web scraping and natural language processing techniques.</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>Procesamiento de Lenguaje Natural, Web Scraping, privacidad de datos, redes sociales</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>qwen2.5:14b-instruct</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:31:13+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2025S12</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>DISEÑO DE UN FORMULARIO WEB PARA LA MEJORA DEL PROCESO DE ONBOARDING Y VALIDACIÓN DE IDENTIDAD EN TRUORA MODALIDAD PASANTÍA</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Lenguaje Golang, MOAT, formulario web, constructor digital</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Este documento detalla el diseño e implementación de un constructor de formularios web en Truora, una empresa tecnológica dedicada a la validación de identidad digital y prevención de fraude. Se identificó la necesidad de esta herramienta debido a que los clientes debían recurrir a proveedores externos para la creación de formularios, lo que impedía a Truora centralizar la captura de información valiosa para el perfilamiento de usuarios. El proyecto se enmarca en la estrategia de Truora para 2024, buscando consolidar su posición como proveedor integral. El alcance incluyo todas las etapas de desarrollo del software, desde el levantamiento detallado de requisitos, el diseño de la arquitectura y la base de datos (utilizando AWS y DynamoDB), hasta el desarrollo del constructor de formularios web con tecnologías como Go (Golang) para el backend y Vue.js 3, TypeScript, Flowbite y Tailwind CSS para el frontend. Se siguió una metodología Scrumban, con colaboración cercana con el equipo de producto y UI/UX. Se desarrolló un Form Builder que permite la creación de secciones y preguntas con diversos tipos de input, reordenamiento de campos y validaciones configurables. Se estableció un flujo para el almacenamiento y consulta de respuestas, visibles en el dashboard de Truora. La validación del funcionamiento e integración se realizó a través de pruebas unitarias y funcionales, tanto en el frontend como en el backend, asegurando la compatibilidad con los sistemas existentes de Truora. Finalmente, se procedió al despliegue y monitoreo en el entorno de producción de AWS.</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>The project focuses on designing and implementing a web form builder for Truora, which is primarily delivered through a web application.</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>formulario web, constructor digital, Golang</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>qwen2.5:14b-instruct</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:31:24+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2025S13</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>DESARROLLO DE APLICACIÓN WEB PARA LA GESTIÓN DE PROYECTOS ÁGILES EN DESARROLLO DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Aplicación web, gestión de proyectos, SCRUM, Kanban, código abierto.</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>En el entorno actual del desarrollo de software, la implementación efectiva de metodologías agiles resulta fundamental para el éxito de los proyectos. Sin embargo, muchas de las herramientas existentes presentan limitaciones en sus versiones gratuitas, lo que afecta especialmente a estudiantes y desarrolladores independientes con recursos limitados. En respuesta a esta problemática, se desarrolló una aplicación web de gestión de proyectos ágil, enfocada en ofrecer una solución gratuita, accesible y funcional. La plataforma permitió la creación y gestión de tableros Kanban, la generación de in formes del backlog, la integración de roles como Product Owner, Scrum Master y Team Member, y la creación de equipos. Además, incluyó funcionalidades como chat integrado, Planning Poker y una interfaz responsive adaptable a distintos dispositivos. El sistema fue diseñado bajo principios de usabilidad y escalabilidad, y se validó mediante pruebas funcionales. Esta herramienta demostró ser una alternativa eficaz frente a soluciones comerciales, permitiendo a equipos agiles mejorar su productividad y coordinación sin restricciones de acceso ni costo. Adicionalmente, la aplicación podría representar una herramienta valiosa en el entorno académico, especialmente en programas como Ingeniería de Sistemas, donde su uso puede ser integrado en cursos relacionados con el desarrollo de software, metodologías agiles o trabajo colaborativo.</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a web application for agile project management, which is the central contribution.</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>Aplicación web, gestión de proyectos, SCRUM, Kanban</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>qwen2.5:14b-instruct</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:31:35+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2025S14</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>PROTOTIPO DE SISTEMA DE RECONOCIMIENTO DE GESTOS DE MANO EN TIEMPO REAL PARA LA INTERACCIÓN HUMANO-COMPUTADORA</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Interación humano maquína, sistema en tiempo real, reconocimiento de gestos, visión por computador, seguimiento, accesibilidad, clasificación.</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>El presente trabajo se centró en el desarrollo de GestOS, un prototipo de reconocimiento de gestos de mano en tiempo real orientado a mejorar la interacción humano-computadora. Su propósito fue ofrecer una alternativa más accesible e inclusiva a los métodos tradicionales de entrada, como el teclado y el mouse, beneficiando tanto a personas con discapacidades como a quienes buscan nuevas formas de interacción. GestOS se construyó con una arquitectura modular compuesta por cuatro capas: presentación (React, TypeScript y Tailwind CSS), aplicación (Electron y Node.js), lógica de negocio (Python, MediaPipe y OpenCV) y acceso al sistema (PyAutoGUI, pynput y otras librerías). Este diseño permitió mantener una estructura escalable, estable y de fácil mantenimiento. El sistema emplea un enfoque híbrido que combina el análisis de puntos clave de la mano con modelos de aprendizaje automático, logrando reconocer siete gestos principales y algunos adicionales con una precisión cercana al 90%. Para evaluar su funcionamiento, se realizaron pruebas funcionales, de rendimiento y de accesibilidad con 43 usuarios, basadas en las normas WCAG 2.1 (nivel AA). Los resultados fueron positivos, aunque se identificaron áreas de mejora, como el rendimiento en condiciones de baja iluminación y la personalización de gestos. GestOS demuestra que la visión artificial puede contribuir significativamente a crear interfaces más naturales e inclusivas. A futuro, se plantea mejorar la precisión, la velocidad de respuesta y permitir el entrenamiento personalizado de gestos, fortaleciendo así la accesibilidad tecnológica.</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Computer vision</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a real-time hand gesture recognition system for human-computer interaction, which falls under computer vision.</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>reconocimiento de gestos, visión por computador, seguimiento</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>qwen2.5:14b-instruct</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:31:47+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2025S15</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>DESARROLLO DE UN PLUGIN PARA LA GESTIÓN DE AMBIENTACIÓN EN ESCENARIOS DE VIDEOJUEGOS UTILIZANDO COMPUTACIÓN EMOCIONAL</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Interacción humano computadora, videojuegos, experiencia emocional, Prototipo integrado en Unity, computación emocional.</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Este trabajo de grado tuvo como objetivo desarrollar un plugin innovador para la gestión emocional de la ambientación en videojuegos, basado en los principios de la computación emocional. En los videojuegos actuales, la ambientación influye directamente en la experiencia emocional, la inmersión y la toma de decisiones del jugador. Por ello, se propuso una herramienta capaz de modificar dinámicamente elementos ambientales, especialmente la iluminación, según las emociones del usuario, generando experiencias más personalizadas e inmersivas. Se construyó un prototipo funcional integrado en Unity, diseñado con un enfoque modular y ligero para facilitar su integración en distintos proyectos sin afectar el rendimiento. La validación se realizó mediante una evaluación con usuarios, quienes visualizaron un video demostrativo y respondieron una encuesta sobre su percepción emocional. Los resultados mostraron que la mayoría identificó correctamente las atmósferas emocionales basadas en la iluminación y valoró positivamente su impacto en la narrativa y la experiencia de juego. El proyecto demostró que es posible modular la experiencia emocional del jugador mediante iluminación controlada, sin alterar la arquitectura ni la narrativa explícita. Además, evidenció que las emociones básicas como alegría y tristeza se interpretan con mayor consistencia, mientras que las más complejas requieren mayor contextualización. Finalmente, se concluyó que la iluminación puede actuar como un canal narrativo autónomo, capaz de evocar emociones y enriquecer la experiencia del jugador, aportando así al avance del campo de la computación emocional aplicada a los videojuegos.</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Serious games</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Natural language processing</t>
+        </is>
+      </c>
+      <c r="H243" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>The project focuses on developing an emotional management plugin for video game scenarios, which aligns with serious games or gamification. However, the emphasis is more on enhancing user experience through emotional computing rather than explicit learning objectives.</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>Interacción humano computadora, videojuegos, experiencia emocional, computación emocional</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>qwen2.5:14b-instruct</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:38:41+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2025S16</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>APLICACIÓN WEB DE ATENCIÓN PARA CONSULTAS DE PROCEDIMIENTOS ADMINISTRATIVOS Y PREGUNTAS FRECUENTES CON INTEGRACIÓN DE UN CHATBOT</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Procesamiento Lenguaje Natural, chatbot, inteligencia artificial, procedimientos administrativos.</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>En este proyecto de trabajo de grado, se desarrolló una aplicación web con información para atender preguntas frecuentes y consultas acerca de algunos procesos administrativos que puedan tener los estudiantes de ingeniería de sistemas de la sede Tuluá, con el apoyo de un asistente virtual (chatbot) para la resolución de dudas acerca de la información requerida, con el fin de reducir el tiempo que usa el personal administrativo en la atención de estos asuntos, incrementando la productividad de los mismos y a su vez dar una respuesta oportuna a dudas o preguntas frecuentes de los alumnos evitando que se desplacen a la oficina o en contra parte, que envíen correos que debido al gran volumen de estos, la respuesta tardará algo de tiempo en llegar. En el desarrollo del proyecto se utilizó inteligencia artificial (IA) para la creación del chatbot incorporando técnicas de procesamiento de lenguaje natural (PLN) para que los estudiantes tengan una interacción fluida y facilidad para dar respuesta a sus cuestionamientos. Además, se adoptó un enfoque web, considerando que actualmente las personas utilizan cada vez más dispositivos inteligentes. Desarrollar una aplicación nativa para cada plataforma puede ser una tarea ardua. Este problema puede ser mitigado significativamente mediante el uso de tecnologías web, ya que permiten que la aplicación sea accesible desde una amplia gama de dispositivos con el único requisito de contar con un navegador web compatible.</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Natural language processing</t>
+        </is>
+      </c>
+      <c r="H244" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a web application with an integrated chatbot using natural language processing techniques.</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>Procesamiento Lenguaje Natural, chatbot, inteligencia artificial, procedimientos administrativos</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>qwen2.5:14b-instruct</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:32:13+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2025S17</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>DISEÑO E IMPLEMENTACIÓN DE UN LAUNCHER ANDROID ENFOCADO A COMBATIR LA PROCRASTINACIÓN POR EL USO EXCESIVO DEL SMARTPHONE EN ESTUDIANTES DE PREGRADO DE LA UNIVERSIDAD DEL VALLE</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Mitigar distracciones, procrastinación, smartphone, telefonos android, launcher.</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Los estudiantes universitarios que hacen un uso excesivo y/o inadecuado del smartphone tienen un menor rendimiento académico e insatisfacción al no gestionar adecuadamente su tiempo e incumplir los plazos de sus actividades pendientes. Dado que el ecosistema de los teléfonos móviles y sus aplicaciones incentiva a pasar el mayor tiempo posible usándolos, se propone desarrollar una pantalla de inicio (launcher) para teléfonos Android que apunte a reducir la procrastinación mediante una interfaz mínimamente llamativa, a mitigar las distracciones y a gestionar mejor el tiempo invertido dentro de las aplicaciones, principalmente en horarios donde se requiera total disposición a una actividad concreta.</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Mobile applications</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>The project focuses on developing an Android launcher to combat procrastination and excessive smartphone use among university students, which aligns with the primary term 'Mobile applications'.</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>Mitigar distracciones, procrastinación, smartphone, telefonos android, launcher</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>qwen2.5:14b-instruct</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:32:26+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2025S18</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>SISTEMA DE OPTIMIZACIÓN DE LA PROGRAMACIÓN ACADÉMICA PARA LA SECCIONAL BUGA</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Sistema de Optimización, programación academica, gestión horaria.</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>El problema estudiado es la gestión ineficiente de horarios y recursos en instituciones educativas, lo que puede provocar conflictos de horarios y una utilización subóptima de los recursos disponibles. Se estudia con el fin de mejorar la eficiencia y la organización en la programación académica. El sistema utiliza algoritmos avanzados para optimizar la distribución de clases, estos algoritmos tienen en cuenta múltiples factores, como la disponibilidad de docentes, requerimientos de asignaturas y características de los salones. Proporcionan una programación académica óptima, minimizando conflictos de horarios y maximizando la utilización de recursos disponibles, a través de una interfaz que permita a los administradores ingresar información relevante. Los resultados obtenidos demuestran que el Sistema de Optimización de Programación Académica es eficaz para mejorar la gestión de horarios y recursos en instituciones educativas. Esto significa que se puede lograr una distribución equitativa de las clases y una utilización más eficiente de los recursos disponibles, lo que contribuye a un funcionamiento más fluido y productivo.</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>The project focuses on optimizing academic scheduling for an educational institution, which falls under enterprise-level management applications.</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>Sistema de Optimización, programación academica, gestión horaria</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>qwen2.5:14b-instruct</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:32:37+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2025S19</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>DESARROLLO DE UN PROTOTIPO DE SOFTWARE USANDO LA GAMIFICACIÓN PARA El APOYO DEL APRENDIZAJE EN LA ASIGNATURA DE CIENCIAS SOCIALES Y EN LA CULTURA GENERAL COLOMBIANA EN NIÑOS DE 5TO GRADO DE PRIMARIA</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Videojuegos, gamificación, ciencias sociales, aprendizaje.</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Este trabajo de grado presenta el desarrollo de un prototipo de videojuego junto a elementos de gamificación, aplicado en el área de Ciencias Sociales y en las competencias de cultura general colombiana, diseñado específicamente para estudiantes de quinto grado de primaria. La propuesta surge como respuesta a la necesidad de generar herramientas innovadoras que despierten el interés de los niños y apoyen su aprendizaje. Durante la etapa de investigación, se realizó un proceso de recopilación y análisis de contenidos educativos a partir de fuentes confiables, planes de estudio oficiales y materiales de libre acceso en línea, ante la dificultad de obtener insumos directamente de las instituciones educativas. Esto permitió construir diálogos, escenarios y dinámicas representativas de cuatro regiones del país: Caribe, Pacífica, Orinoquía y Amazonía. La implementación técnica se llevó a cabo utilizando un motor gráfico apoyado en herramientas para el modelado 3D, las animaciones de personajes, la generación de texturas y bibliotecas de sonido de libre uso. El videojuego fue diseñado con una estructura modular de misiones, cada una con objetivos específicos y personajes interactivos que fomentan la exploración. La fase de pruebas incluyó la aplicación del prototipo en un grupo real de estudiantes, mediante observación directa y entrevistas estructuradas tanto a los niños como a su docente. Los resultados muestran un alto nivel de motivación, participación activa y comprensión temática por parte de los estudiantes, validando la efectividad del enfoque lúdico para el aprendizaje de las Ciencias Sociales y la cultura general. Este proyecto demostró la viabilidad técnica y pedagógica de integrar el desarrollo de software con la educación primaria, proponiendo un modelo replicable que puede ser ampliado y mejorado en futuras investigaciones. Así, se reafirma el potencial de los videojuegos como herramientas educativas valiosas en contextos escolares</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Gamification</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a game prototype with gamification elements to support learning in social sciences and Colombian general culture for fifth-grade students, clearly aligning with the concept of gamification.</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>Videojuegos, gamificación, ciencias sociales, aprendizaje</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>qwen2.5:14b-instruct</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:32:50+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2025S20</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>DESARROLLO DE UN PROTOTIPO DE APLICACIÓN WEB PARA LA IMPLEMENTACIÓN DE UN SISTEMA DE RECOMENDACIÓN DE ROPA BASADO EN EL BIENESTAR EMOCIONAL DEL USUARIO MEDIANTE LA INTEGRACIÓN DE LA ECONOMÍA CONDUCTUAL</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Clothing recommendation system, Prototype web application, Human computer interaction, user interfaces, Sentiment analysis.</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>En la ingeniería de sistemas, el diseño de aplicaciones web suele centrarse en aspectos técnicos, dejando de lado las emociones del usuario. Esta limitación es particularmente evidente en las plataformas de recomendación de ropa, donde la falta de empatía genera experiencias impersonales y desconectadas emocionalmente. Como resultado, se afecta la toma de decisiones, la fidelización y la satisfacción de los usuarios. Este trabajo de grado propuso el desarrollo de un prototipo de aplicación web que incorpora el análisis emocional del usuario y principios de la Economía Conductual para ofrecer recomendaciones de ropa más humanas, personalizadas y emocionalmente relevantes. El objetivo no fue solo facilitar la elección de una prenda, sino también atender el estado emocional de cada individuo y reconocer su influencia en la interacción con la tecnología. La propuesta se construyó desde un enfoque interdisciplinario, integrando psicología del usuario, interacción humano-computadora y bienestar digital. Se trabajó con conceptos como inteligencia emocional, modelado de estados afectivos y toma de decisiones influenciada por emociones. Los resultados del prototipo demostraron que incluir elementos emocionales mejora la experiencia digital, fomenta la personalización y permite construir plataformas más sensibles y alineadas con las necesidades reales del usuario. Este enfoque contribuye a una visión más humana de la tecnología y plantea nuevas posibilidades para el diseño digital en la moda y otros sectores.</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Recommender systems</t>
+        </is>
+      </c>
+      <c r="H248" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a web application prototype that integrates sentiment analysis and behavioral economics to provide personalized clothing recommendations based on the user's emotional well-being.</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>Clothing recommendation system, Prototype web application, Sentiment analysis</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>qwen2.5:14b-instruct</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:33:03+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2025S21</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>PROTOTIPO DE SISTEMA DE DETECCION TEMPRANA DE SOFTWARE MALINTENCIONADO POR MEDIO DE COMPORTAMIENTOS ANÓMALOS EN WINDOWS 10</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Ransomware de cifrado, ciberseguridad, ciberataque, integridad de datos.</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Este proyecto se realizó con el objetivo de desarrollar un prototipo de sistema para la detección temprana de comportamientos anómalos en el sistema operativo Windows 10, con el fin de prevenir posibles ataques de ransomware de cifrado y la pérdida de datos que estos conllevan. La justificación de este trabajo radica en la necesidad de herramientas que permitan identificar patrones de comportamiento sospechosos en sistemas informáticos, específicamente en Windows 10, lo que posibilitará recolectar la información necesaria para detectar cuándo se está ejecutando un ataque de ransomware y desplegar una respuesta efectiva en el sistema operativo, reduciendo significativamente el riesgo de pérdida de información. Finalmente, se consiguió desarrollar un prototipo de detección funcional con un alto nivel de asertividad en la detección de comportamientos anómalos por medio de la aplicación de puntaje por entropía, lo cuál cumple con los objetivos planteados.</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a prototype for early detection of malicious software behavior in Windows 10 to prevent ransomware attacks, which falls under cybersecurity.</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>Ransomware de cifrado, ciberseguridad, ciberataque, integridad de datos</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>qwen2.5:14b-instruct</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:33:16+00:00</t>
         </is>
       </c>
     </row>
